--- a/output/yearly_surface_area_iteration_58_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_58_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497617754444</v>
+        <v>10.84497630571843</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907140296326</v>
+        <v>37.78907184958262</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.011421119552467</v>
+        <v>4.98335134675681</v>
       </c>
       <c r="C2" t="n">
-        <v>14.14502092278804</v>
+        <v>6.71908128786517</v>
       </c>
       <c r="D2" t="n">
-        <v>26.4698816019025</v>
+        <v>21.07223272395354</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.46819584393449</v>
+        <v>16.63080610994097</v>
       </c>
       <c r="C3" t="n">
-        <v>43.08399800087128</v>
+        <v>29.08918447683299</v>
       </c>
       <c r="D3" t="n">
-        <v>97.17829650487053</v>
+        <v>67.46570223584081</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.79720449804419</v>
+        <v>35.08471770666826</v>
       </c>
       <c r="C4" t="n">
-        <v>114.0221418666331</v>
+        <v>66.8511281729823</v>
       </c>
       <c r="D4" t="n">
-        <v>119.7526032163217</v>
+        <v>94.09953570435253</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.31837366027901</v>
+        <v>43.04963683122264</v>
       </c>
       <c r="C5" t="n">
-        <v>159.8039825587746</v>
+        <v>122.4730261047896</v>
       </c>
       <c r="D5" t="n">
-        <v>84.38121518001337</v>
+        <v>70.71037839837653</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.63780151705772</v>
+        <v>38.68184129502858</v>
       </c>
       <c r="C6" t="n">
-        <v>173.8871533761951</v>
+        <v>154.6468618683661</v>
       </c>
       <c r="D6" t="n">
-        <v>54.33973543006097</v>
+        <v>47.81896717845365</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.31963314542373</v>
+        <v>27.18852092141116</v>
       </c>
       <c r="C7" t="n">
-        <v>168.2214873749867</v>
+        <v>129.8341703912322</v>
       </c>
       <c r="D7" t="n">
-        <v>40.18391528252619</v>
+        <v>38.98618308334508</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.26555490623215</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>112.9058947269044</v>
+        <v>88.8727109269425</v>
       </c>
       <c r="D8" t="n">
-        <v>35.549084370777</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>55.24687030878498</v>
+        <v>50.03280825153018</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
         <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>26.4698816019025</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.45533531278805</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.601230428052157</v>
+        <v>7.659058415800023</v>
       </c>
       <c r="C21" t="n">
-        <v>90.26461133311936</v>
+        <v>92.86608329157528</v>
       </c>
       <c r="D21" t="n">
-        <v>7.601230428052157</v>
+        <v>7.659058415800023</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.006512381031233</v>
+        <v>5.241550992973721</v>
       </c>
       <c r="C2" t="n">
-        <v>16.55030279819273</v>
+        <v>12.04506258340412</v>
       </c>
       <c r="D2" t="n">
-        <v>29.20110371511713</v>
+        <v>24.74691438094935</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.62527547661398</v>
+        <v>16.47372647726148</v>
       </c>
       <c r="C3" t="n">
-        <v>48.05655012288137</v>
+        <v>27.42021337961341</v>
       </c>
       <c r="D3" t="n">
-        <v>95.17553118820703</v>
+        <v>67.88785374866693</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.37228766855457</v>
+        <v>32.96610616090365</v>
       </c>
       <c r="C4" t="n">
-        <v>109.7083424541726</v>
+        <v>68.85487523735006</v>
       </c>
       <c r="D4" t="n">
-        <v>134.0979006707761</v>
+        <v>102.8164735703599</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.60093707265284</v>
+        <v>47.07480241863456</v>
       </c>
       <c r="C5" t="n">
-        <v>179.4880240289231</v>
+        <v>121.4912784005428</v>
       </c>
       <c r="D5" t="n">
-        <v>102.8135283272472</v>
+        <v>85.48568134729102</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.27932473628739</v>
+        <v>47.2956956520901</v>
       </c>
       <c r="C6" t="n">
-        <v>207.8998025898258</v>
+        <v>173.5651401292021</v>
       </c>
       <c r="D6" t="n">
-        <v>64.36239774271665</v>
+        <v>56.51332484726341</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.72750041104266</v>
+        <v>35.99185258539232</v>
       </c>
       <c r="C7" t="n">
-        <v>201.9376487819349</v>
+        <v>171.6949107526119</v>
       </c>
       <c r="D7" t="n">
-        <v>45.33416373900496</v>
+        <v>43.29801900039708</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.93867397844697</v>
+        <v>20.9455872701057</v>
       </c>
       <c r="C8" t="n">
-        <v>158.135011461555</v>
+        <v>127.5928403824367</v>
       </c>
       <c r="D8" t="n">
-        <v>37.38495257771854</v>
+        <v>37.55184968744049</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.431249284071605</v>
+        <v>10.31718662392973</v>
       </c>
       <c r="C9" t="n">
-        <v>90.52499231318986</v>
+        <v>76.87968097186344</v>
       </c>
       <c r="D9" t="n">
-        <v>34.61249706092553</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>45.12603322570465</v>
+        <v>44.4142661401257</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>31.62994753542373</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.27567548291088</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.757534411091656</v>
+        <v>7.832809522194543</v>
       </c>
       <c r="C21" t="n">
-        <v>97.93887194003217</v>
+        <v>100.8474225982547</v>
       </c>
       <c r="D21" t="n">
-        <v>8.727226212478113</v>
+        <v>8.811910712468862</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.396266219617217</v>
+        <v>7.738135404873359</v>
       </c>
       <c r="C2" t="n">
-        <v>11.24297470903447</v>
+        <v>17.26108813606742</v>
       </c>
       <c r="D2" t="n">
-        <v>29.76953563587603</v>
+        <v>25.90243142884784</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.49273953654066</v>
+        <v>16.59644494029233</v>
       </c>
       <c r="C3" t="n">
-        <v>54.1581121047753</v>
+        <v>35.9368747139545</v>
       </c>
       <c r="D3" t="n">
-        <v>94.92518552362409</v>
+        <v>70.24404823885929</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.91733757086079</v>
+        <v>31.47286790274425</v>
       </c>
       <c r="C4" t="n">
-        <v>112.2225983247486</v>
+        <v>67.78280674431252</v>
       </c>
       <c r="D4" t="n">
-        <v>145.2525180864283</v>
+        <v>109.3126981293611</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.25732537616646</v>
+        <v>48.13018120069989</v>
       </c>
       <c r="C5" t="n">
-        <v>187.538355203747</v>
+        <v>123.4547738090364</v>
       </c>
       <c r="D5" t="n">
-        <v>118.0306177430728</v>
+        <v>99.03379966589702</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.38499363544755</v>
+        <v>53.49445065670446</v>
       </c>
       <c r="C6" t="n">
-        <v>234.948915337234</v>
+        <v>180.4481732836765</v>
       </c>
       <c r="D6" t="n">
-        <v>76.51839781670066</v>
+        <v>66.45548384817086</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.95570784678443</v>
+        <v>44.01665831990574</v>
       </c>
       <c r="C7" t="n">
-        <v>237.7498415374501</v>
+        <v>203.8540203006247</v>
       </c>
       <c r="D7" t="n">
-        <v>50.30475236560656</v>
+        <v>48.44826745687584</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.9455872701057</v>
+        <v>28.12216298814988</v>
       </c>
       <c r="C8" t="n">
-        <v>198.7744576788517</v>
+        <v>170.1516033615359</v>
       </c>
       <c r="D8" t="n">
-        <v>39.97185777840888</v>
+        <v>39.63806355896497</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.09374905798895</v>
+        <v>14.64374875654542</v>
       </c>
       <c r="C9" t="n">
-        <v>129.4640515067311</v>
+        <v>109.7171781835107</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>68.04493338134642</v>
+        <v>63.06256378229386</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>38.73780091417063</v>
+        <v>40.33706792438868</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.24313893995049</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.896189029028152</v>
+        <v>7.990751787984228</v>
       </c>
       <c r="C21" t="n">
-        <v>104.624504634623</v>
+        <v>107.8751491377871</v>
       </c>
       <c r="D21" t="n">
-        <v>8.883212657656671</v>
+        <v>9.988439734980284</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.158683275189489</v>
+        <v>6.961572970814132</v>
       </c>
       <c r="C2" t="n">
-        <v>8.184830610305658</v>
+        <v>12.01364665686822</v>
       </c>
       <c r="D2" t="n">
-        <v>24.90890275215007</v>
+        <v>21.39620946635499</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.28581175512284</v>
+        <v>20.63142800474672</v>
       </c>
       <c r="C3" t="n">
-        <v>75.92836744644832</v>
+        <v>54.48699758569798</v>
       </c>
       <c r="D3" t="n">
-        <v>103.8934508019187</v>
+        <v>76.97392875147118</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.89333365760237</v>
+        <v>23.11328620108265</v>
       </c>
       <c r="C4" t="n">
-        <v>149.6301310996649</v>
+        <v>98.05597895246717</v>
       </c>
       <c r="D4" t="n">
-        <v>135.6294270894011</v>
+        <v>106.9515949006475</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.8564692131975</v>
+        <v>30.11511082777092</v>
       </c>
       <c r="C5" t="n">
-        <v>140.3899217072939</v>
+        <v>107.820441618906</v>
       </c>
       <c r="D5" t="n">
-        <v>75.17733045269952</v>
+        <v>66.31705742187205</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.05161602216436</v>
+        <v>27.33087433852696</v>
       </c>
       <c r="C6" t="n">
-        <v>156.5789413503238</v>
+        <v>134.2392723401876</v>
       </c>
       <c r="D6" t="n">
-        <v>33.12711278440013</v>
+        <v>31.87931145230244</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.83380690054181</v>
+        <v>18.62473569726624</v>
       </c>
       <c r="C7" t="n">
-        <v>139.7753476444354</v>
+        <v>119.6534466981928</v>
       </c>
       <c r="D7" t="n">
-        <v>28.086820070797</v>
+        <v>27.84727363096077</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>95.38169820609886</v>
+        <v>80.86164966028853</v>
       </c>
       <c r="D8" t="n">
-        <v>26.11939767148639</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>51.9187455913883</v>
+        <v>48.14687091167205</v>
       </c>
       <c r="D9" t="n">
-        <v>26.73593522975338</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.4164820107789</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>25.05518316008284</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>27.8983245115816</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.952696183746906</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>22.99842171968578</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>26.25291535926396</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.040652566501619</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>21.5935407549086</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6145740628585034</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>8.425358797846126</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>71.28470080536088</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>6.052474596681584</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.577087723647877</v>
+        <v>4.169482499936204</v>
       </c>
       <c r="C2" t="n">
-        <v>4.412955930589413</v>
+        <v>5.517422097867075</v>
       </c>
       <c r="D2" t="n">
-        <v>17.46529165855076</v>
+        <v>15.20432669567035</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.10418842983718</v>
+        <v>22.63419332141021</v>
       </c>
       <c r="C3" t="n">
-        <v>56.2050560681299</v>
+        <v>51.74792149084938</v>
       </c>
       <c r="D3" t="n">
-        <v>101.7139708984908</v>
+        <v>77.35681035612743</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.19437034990764</v>
+        <v>30.04344324536089</v>
       </c>
       <c r="C4" t="n">
-        <v>172.4371120170225</v>
+        <v>118.5146193612665</v>
       </c>
       <c r="D4" t="n">
-        <v>152.1826751307066</v>
+        <v>118.1445004767654</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.99177046993431</v>
+        <v>33.57577148524092</v>
       </c>
       <c r="C5" t="n">
-        <v>196.5949777754238</v>
+        <v>143.3106211274282</v>
       </c>
       <c r="D5" t="n">
-        <v>93.9287116038136</v>
+        <v>83.59581701661591</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.35225180384214</v>
+        <v>32.08056973167303</v>
       </c>
       <c r="C6" t="n">
-        <v>188.8607693613675</v>
+        <v>156.7399479738203</v>
       </c>
       <c r="D6" t="n">
-        <v>40.6139207769863</v>
+        <v>39.04410619789565</v>
       </c>
     </row>
     <row r="7">
@@ -2094,10 +2094,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.69596131131975</v>
+        <v>17.36711688812607</v>
       </c>
       <c r="C7" t="n">
-        <v>171.6350241426528</v>
+        <v>149.3572052378842</v>
       </c>
       <c r="D7" t="n">
         <v>30.3625112492411</v>
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.508987279156353</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>122.419029981056</v>
+        <v>106.56380455747</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8704346652352</v>
+        <v>27.78836876870596</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.882812170296134</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>52.58437053486764</v>
+        <v>52.47343304428775</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.421570675749381</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6508987279156353</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>24.71549845441346</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>61.98656829843935</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>4.814490741626358</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.084250376115978</v>
+        <v>3.950552761889165</v>
       </c>
       <c r="C2" t="n">
-        <v>4.608323723734528</v>
+        <v>6.684720118216532</v>
       </c>
       <c r="D2" t="n">
-        <v>23.4078105123567</v>
+        <v>14.99423268696153</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.12458414744811</v>
+        <v>18.57466656434965</v>
       </c>
       <c r="C3" t="n">
-        <v>37.42913122440964</v>
+        <v>36.09395434663399</v>
       </c>
       <c r="D3" t="n">
-        <v>93.19730956414971</v>
+        <v>71.9768329368549</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.6703380600181</v>
+        <v>35.91429451675682</v>
       </c>
       <c r="C4" t="n">
-        <v>157.223949592014</v>
+        <v>123.7345719047467</v>
       </c>
       <c r="D4" t="n">
-        <v>164.7922426440526</v>
+        <v>128.0866594776729</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.03518835309942</v>
+        <v>38.85266539556753</v>
       </c>
       <c r="C5" t="n">
-        <v>249.5357227269331</v>
+        <v>180.6661212740193</v>
       </c>
       <c r="D5" t="n">
-        <v>119.6750451476862</v>
+        <v>103.1080526385213</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.57867567062465</v>
+        <v>37.95731148929444</v>
       </c>
       <c r="C6" t="n">
-        <v>241.026915374226</v>
+        <v>189.0620276407381</v>
       </c>
       <c r="D6" t="n">
-        <v>55.30577517103983</v>
+        <v>52.60891422747383</v>
       </c>
     </row>
     <row r="7">
@@ -2405,10 +2405,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.50496247734813</v>
+        <v>25.63146906247572</v>
       </c>
       <c r="C7" t="n">
-        <v>216.070888732272</v>
+        <v>186.0676971427852</v>
       </c>
       <c r="D7" t="n">
         <v>33.83593462686632</v>
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C8" t="n">
-        <v>165.895727063626</v>
+        <v>147.3701478844887</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37250865273282</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>89.74842987913063</v>
+        <v>85.19999276535516</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>43.13308538608361</v>
+        <v>45.26838664282043</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.421570675749381</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6508987279156353</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.43093048890212</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2565,7 +2565,7 @@
         <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>6.42062998577414</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31.89600116327462</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>3.009056713516474</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.293943474197296</v>
+        <v>2.364048471826319</v>
       </c>
       <c r="C2" t="n">
-        <v>2.347358760854124</v>
+        <v>3.204424506661589</v>
       </c>
       <c r="D2" t="n">
-        <v>16.55717503212246</v>
+        <v>10.44383207777757</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.39809084630547</v>
+        <v>18.34886459237289</v>
       </c>
       <c r="C3" t="n">
-        <v>32.32895190084746</v>
+        <v>34.17463758483147</v>
       </c>
       <c r="D3" t="n">
-        <v>93.54582999915732</v>
+        <v>70.67110849020665</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.77618688562751</v>
+        <v>39.44956799974958</v>
       </c>
       <c r="C4" t="n">
-        <v>152.3613532128795</v>
+        <v>123.568656542729</v>
       </c>
       <c r="D4" t="n">
-        <v>175.4363512534965</v>
+        <v>135.9484950932813</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.0414797499524</v>
+        <v>40.54618018539328</v>
       </c>
       <c r="C5" t="n">
-        <v>300.9056713516474</v>
+        <v>222.3658550119026</v>
       </c>
       <c r="D5" t="n">
-        <v>121.4912784005428</v>
+        <v>108.5322087044849</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.01765576314322</v>
+        <v>30.99377502307181</v>
       </c>
       <c r="C6" t="n">
-        <v>269.1628228302353</v>
+        <v>225.3287695833195</v>
       </c>
       <c r="D6" t="n">
-        <v>53.45419900083034</v>
+        <v>51.44161620712438</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.809001166028376</v>
+        <v>7.964919124554372</v>
       </c>
       <c r="C7" t="n">
-        <v>218.5262397405933</v>
+        <v>192.8947706781175</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>33.89582123682538</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.171045084717197</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>109.9851953067702</v>
+        <v>106.0631132283042</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>32.8374972116473</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>30.61874740004951</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9964739198105126</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>24.20008090968388</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>22.91890015564179</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>17.94732978133594</v>
+        <v>19.90198946049134</v>
       </c>
       <c r="D11" t="n">
-        <v>22.38973814305275</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.10280577150543</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>14.82929907264807</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2862,7 +2862,7 @@
         <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>5.194427103169874</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27.28767743954009</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>2.140209995258047</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.679770321966293</v>
+        <v>2.589850443803086</v>
       </c>
       <c r="C2" t="n">
-        <v>4.019275101186442</v>
+        <v>6.889905388404116</v>
       </c>
       <c r="D2" t="n">
-        <v>13.84264262988003</v>
+        <v>10.94648690235194</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.22704576158827</v>
+        <v>13.47448724078747</v>
       </c>
       <c r="C3" t="n">
-        <v>21.60335823195106</v>
+        <v>23.33614292994668</v>
       </c>
       <c r="D3" t="n">
-        <v>86.26617077216723</v>
+        <v>63.67124735892688</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.33850733598268</v>
+        <v>37.29266829351933</v>
       </c>
       <c r="C4" t="n">
-        <v>120.3396883434613</v>
+        <v>106.185831691335</v>
       </c>
       <c r="D4" t="n">
-        <v>179.8522524271987</v>
+        <v>139.1519378522387</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.01755795215198</v>
+        <v>48.44924920458011</v>
       </c>
       <c r="C5" t="n">
-        <v>294.3279617331938</v>
+        <v>224.3293504203962</v>
       </c>
       <c r="D5" t="n">
-        <v>146.7958254775043</v>
+        <v>127.2345024703866</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.37741739125406</v>
+        <v>40.21140421824511</v>
       </c>
       <c r="C6" t="n">
-        <v>353.5705451982633</v>
+        <v>285.2232335240089</v>
       </c>
       <c r="D6" t="n">
-        <v>71.48694083243576</v>
+        <v>68.26680836250623</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.31856928226148</v>
+        <v>16.94791061841269</v>
       </c>
       <c r="C7" t="n">
-        <v>284.7608303553085</v>
+        <v>249.0684108197115</v>
       </c>
       <c r="D7" t="n">
-        <v>38.08788393395925</v>
+        <v>38.50709020367265</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>176.0764507566654</v>
+        <v>165.4784842893211</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>32.7952820603647</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>64.5656195174957</v>
+        <v>68.89218165011141</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>24.05772749256809</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1776963344686726</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>20.7904711328347</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>14.82929907264807</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>24.38563122578652</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>3.777765165941727</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.038689071093125</v>
+        <v>1.748492661263569</v>
       </c>
       <c r="C2" t="n">
-        <v>2.889283493598362</v>
+        <v>3.657991946023615</v>
       </c>
       <c r="D2" t="n">
-        <v>10.39867168338222</v>
+        <v>8.598146393793566</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.269841749947631</v>
+        <v>11.67298020349457</v>
       </c>
       <c r="C3" t="n">
-        <v>19.49260066782042</v>
+        <v>25.06401888942107</v>
       </c>
       <c r="D3" t="n">
-        <v>80.07134275836985</v>
+        <v>59.30737881354982</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.73491242432013</v>
+        <v>33.74463209037137</v>
       </c>
       <c r="C4" t="n">
-        <v>97.3412666237755</v>
+        <v>89.10931212366599</v>
       </c>
       <c r="D4" t="n">
-        <v>181.2306262039612</v>
+        <v>139.5475821770501</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.76016012719008</v>
+        <v>52.20443417332415</v>
       </c>
       <c r="C5" t="n">
-        <v>279.5772024768855</v>
+        <v>221.3104762298373</v>
       </c>
       <c r="D5" t="n">
-        <v>164.2463909204914</v>
+        <v>140.6108149407494</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.67805317293184</v>
+        <v>46.89317909334891</v>
       </c>
       <c r="C6" t="n">
-        <v>402.2750488059476</v>
+        <v>321.1679622195974</v>
       </c>
       <c r="D6" t="n">
-        <v>83.40143097117505</v>
+        <v>79.57752366313373</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.941177253203202</v>
+        <v>15.15131231964102</v>
       </c>
       <c r="C7" t="n">
-        <v>351.4146272397373</v>
+        <v>303.0861330027795</v>
       </c>
       <c r="D7" t="n">
-        <v>42.33983324105218</v>
+        <v>42.99858595060179</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.171045084717197</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>219.5531478392354</v>
+        <v>211.2917409079985</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.220312396378785</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>63.34530712111692</v>
+        <v>75.43749359432489</v>
       </c>
       <c r="D9" t="n">
-        <v>30.7296848906294</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1423534171157875</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>25.48126166372597</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>18.87606310955342</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.6666888066416</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.00334615374024</v>
+        <v>3.067961575771282</v>
       </c>
       <c r="C2" t="n">
-        <v>6.968445204743859</v>
+        <v>13.12105806725862</v>
       </c>
       <c r="D2" t="n">
-        <v>13.20647011752809</v>
+        <v>8.330129270534187</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5.581235698643117</v>
+        <v>8.978082755337082</v>
       </c>
       <c r="C3" t="n">
-        <v>16.03684874887165</v>
+        <v>20.00310947402876</v>
       </c>
       <c r="D3" t="n">
-        <v>72.28117472517141</v>
+        <v>54.11884219660542</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.11029990024091</v>
+        <v>28.58849314766712</v>
       </c>
       <c r="C4" t="n">
-        <v>77.83983022661685</v>
+        <v>77.36760958087413</v>
       </c>
       <c r="D4" t="n">
-        <v>177.3379965566226</v>
+        <v>135.9229696529709</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.80295611554943</v>
+        <v>51.44357970253288</v>
       </c>
       <c r="C5" t="n">
-        <v>238.2456241280948</v>
+        <v>197.0367642423349</v>
       </c>
       <c r="D5" t="n">
-        <v>182.2369176008142</v>
+        <v>153.4962535589888</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.87051678069322</v>
+        <v>55.34602682691394</v>
       </c>
       <c r="C6" t="n">
-        <v>418.61722109084</v>
+        <v>334.1692470669379</v>
       </c>
       <c r="D6" t="n">
-        <v>103.7687688434794</v>
+        <v>97.36875555949442</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.66654993792135</v>
+        <v>28.02693346083794</v>
       </c>
       <c r="C7" t="n">
-        <v>436.9925928712275</v>
+        <v>369.2608370075358</v>
       </c>
       <c r="D7" t="n">
-        <v>50.66407202536089</v>
+        <v>51.38271134486956</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>301.4996287127167</v>
+        <v>281.4719755460818</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>128.7984265632518</v>
+        <v>140.55780056472</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>42.56367171762047</v>
+        <v>50.82016991033614</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>19.30999559483051</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>24.38563122578652</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>2.479894700927443</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.590652265058085</v>
+        <v>5.458517235612265</v>
       </c>
       <c r="C2" t="n">
-        <v>15.27108553955914</v>
+        <v>11.54535300194249</v>
       </c>
       <c r="D2" t="n">
-        <v>23.99980437801753</v>
+        <v>7.127488332831843</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7471100029318227</v>
+        <v>2.242311756499715</v>
       </c>
       <c r="C2" t="n">
-        <v>4.236241343824987</v>
+        <v>7.662540831646355</v>
       </c>
       <c r="D2" t="n">
-        <v>9.930378028456486</v>
+        <v>6.196791509205867</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.466191290796992</v>
+        <v>12.40438224315845</v>
       </c>
       <c r="C3" t="n">
-        <v>22.31021657900877</v>
+        <v>31.6417285078747</v>
       </c>
       <c r="D3" t="n">
-        <v>78.45145904636263</v>
+        <v>58.30108741669683</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.81898287398687</v>
+        <v>39.3219407981975</v>
       </c>
       <c r="C4" t="n">
-        <v>118.1317377566102</v>
+        <v>112.1970728844382</v>
       </c>
       <c r="D4" t="n">
-        <v>178.5632176915226</v>
+        <v>139.2029887328595</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.76396394482004</v>
+        <v>31.63681976935347</v>
       </c>
       <c r="C5" t="n">
-        <v>356.6934846454724</v>
+        <v>288.58473766335</v>
       </c>
       <c r="D5" t="n">
-        <v>161.6938468894497</v>
+        <v>140.1690284738384</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.94845039776043</v>
+        <v>17.38871533761951</v>
       </c>
       <c r="C6" t="n">
-        <v>349.3441213314808</v>
+        <v>302.1691806470131</v>
       </c>
       <c r="D6" t="n">
-        <v>78.16871570753956</v>
+        <v>76.1963845697077</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.353650157707104</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>211.9985992550562</v>
+        <v>197.9252459146782</v>
       </c>
       <c r="D7" t="n">
-        <v>30.30262463928205</v>
+        <v>32.15910954801276</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.084831213192726</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>94.88100687693299</v>
+        <v>103.5596565824748</v>
       </c>
       <c r="D8" t="n">
-        <v>23.11524969649115</v>
+        <v>24.11663235482289</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1109374905798895</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>32.50468473990763</v>
+        <v>38.71718421238145</v>
       </c>
       <c r="D9" t="n">
-        <v>19.30312336090078</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>18.93300447639974</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>18.50594422505238</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>13.68261775408779</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
-        <v>15.45958109877452</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>9.76348091873453</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>18.12993485432585</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>1.791689560250429</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.772676500971245</v>
+        <v>6.284167054883833</v>
       </c>
       <c r="C2" t="n">
-        <v>11.4952838690259</v>
+        <v>5.033420479673397</v>
       </c>
       <c r="D2" t="n">
-        <v>26.27647730416588</v>
+        <v>19.81068692399639</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.572040116406402</v>
+        <v>11.59934912567607</v>
       </c>
       <c r="C3" t="n">
-        <v>38.47960126795374</v>
+        <v>29.09409321535422</v>
       </c>
       <c r="D3" t="n">
-        <v>23.29687302177681</v>
+        <v>9.125344910974103</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.43525839034661</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4585,7 +4585,7 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.90042687571034</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
         <v>32.21899615797182</v>
@@ -4596,10 +4596,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>21.52972715413255</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D8" t="n">
         <v>35.79943003535994</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.930157044278233</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
         <v>27.36523550817559</v>
@@ -4658,7 +4658,7 @@
         <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
-        <v>43.61021477034756</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -4672,7 +4672,7 @@
         <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4694,7 +4694,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
         <v>26.15866757965626</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39448779722202</v>
+        <v>13.3978592400621</v>
       </c>
       <c r="C21" t="n">
-        <v>70.12408317369173</v>
+        <v>70.14173366856043</v>
       </c>
       <c r="D21" t="n">
-        <v>1.575822093790825</v>
+        <v>1.576218734124953</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.137084825696059</v>
+        <v>4.928373475318988</v>
       </c>
       <c r="C2" t="n">
-        <v>6.732825755724625</v>
+        <v>5.230751768227005</v>
       </c>
       <c r="D2" t="n">
-        <v>26.93523001371549</v>
+        <v>26.63874220703295</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.61960597456675</v>
+        <v>17.66164119940012</v>
       </c>
       <c r="C3" t="n">
-        <v>42.36241343824987</v>
+        <v>23.17415455874596</v>
       </c>
       <c r="D3" t="n">
-        <v>38.91157025782233</v>
+        <v>23.55703616340222</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.03975293425538</v>
+        <v>13.54124608467625</v>
       </c>
       <c r="C4" t="n">
-        <v>58.21076662790613</v>
+        <v>44.8737240657132</v>
       </c>
       <c r="D4" t="n">
-        <v>26.69961056469625</v>
+        <v>19.84602984134927</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.117048960983624</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4879,10 +4879,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.58368222013712</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4910,10 +4910,10 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.45180923259856</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.4046853427947</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.04843409934012</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4952,10 +4952,10 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>48.33340297547896</v>
+        <v>47.97801030654161</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.292021036517808</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>44.47807974090174</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.48789721794422</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4994,7 +4994,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>44.86390658867074</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.36098972218912</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.428568847467</v>
+        <v>15.43868517439593</v>
       </c>
       <c r="C21" t="n">
-        <v>86.07517357007909</v>
+        <v>86.13161202557728</v>
       </c>
       <c r="D21" t="n">
-        <v>3.248119757361475</v>
+        <v>3.250249510399143</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.268639018065131</v>
+        <v>4.710425484976196</v>
       </c>
       <c r="C2" t="n">
-        <v>6.489352325071417</v>
+        <v>12.11967540892687</v>
       </c>
       <c r="D2" t="n">
-        <v>25.99275221763855</v>
+        <v>27.23269956810227</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.85875150377547</v>
+        <v>17.33275571847744</v>
       </c>
       <c r="C3" t="n">
-        <v>32.83455196853458</v>
+        <v>21.47573103039898</v>
       </c>
       <c r="D3" t="n">
-        <v>50.72690387843269</v>
+        <v>39.40244410994573</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.6838615436993</v>
+        <v>25.28294862746811</v>
       </c>
       <c r="C4" t="n">
-        <v>84.84656359182634</v>
+        <v>52.07189823325082</v>
       </c>
       <c r="D4" t="n">
-        <v>39.20707631680062</v>
+        <v>27.18459393059418</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.891108120286615</v>
+        <v>11.95277829920492</v>
       </c>
       <c r="C5" t="n">
-        <v>62.61095983834034</v>
+        <v>49.57825906446394</v>
       </c>
       <c r="D5" t="n">
-        <v>32.49584901056943</v>
+        <v>29.82058651649687</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.997496725243765</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.47801332097696</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5207,7 +5207,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.29044275620359</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>40.60312155223957</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.39663573917827</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>49.22188464782232</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
-        <v>45.99684343937156</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5364,7 +5364,7 @@
         <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.70670275981679</v>
+        <v>16.72743897952156</v>
       </c>
       <c r="C21" t="n">
-        <v>101.0755516968916</v>
+        <v>102.0373777750815</v>
       </c>
       <c r="D21" t="n">
-        <v>4.176675689954196</v>
+        <v>4.18185974488039</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.73104218676538</v>
+        <v>5.308309836862503</v>
       </c>
       <c r="C2" t="n">
-        <v>12.36805757810132</v>
+        <v>9.602474295238052</v>
       </c>
       <c r="D2" t="n">
-        <v>32.08744196560275</v>
+        <v>26.80760281216341</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.64276700884118</v>
+        <v>16.64062358698343</v>
       </c>
       <c r="C3" t="n">
-        <v>28.51486206984861</v>
+        <v>35.9368747139545</v>
       </c>
       <c r="D3" t="n">
-        <v>58.64469911318322</v>
+        <v>51.33558745506572</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.33399950808894</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="C4" t="n">
-        <v>83.34056261351174</v>
+        <v>52.46754255806228</v>
       </c>
       <c r="D4" t="n">
-        <v>53.64171281234147</v>
+        <v>40.0749412873548</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.56761440397068</v>
+        <v>24.93639168786899</v>
       </c>
       <c r="C5" t="n">
-        <v>110.8884031946773</v>
+        <v>74.73554398578845</v>
       </c>
       <c r="D5" t="n">
-        <v>38.90175278077987</v>
+        <v>32.49584901056943</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.539642442166258</v>
+        <v>10.94845039776043</v>
       </c>
       <c r="C6" t="n">
-        <v>56.47307319138928</v>
+        <v>46.57116584635595</v>
       </c>
       <c r="D6" t="n">
-        <v>38.03781480104267</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.61906619521901</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>39.80496066868692</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.61405964570653</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>49.93266998569701</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5591,7 +5591,7 @@
         <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.1711936201</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.00959105494056</v>
+        <v>18.04469539760044</v>
       </c>
       <c r="C21" t="n">
-        <v>115.7759424960465</v>
+        <v>117.7201556891076</v>
       </c>
       <c r="D21" t="n">
-        <v>6.003197018313521</v>
+        <v>6.014898465866811</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.46637121724624</v>
+        <v>6.685701865920779</v>
       </c>
       <c r="C2" t="n">
-        <v>14.77824819202724</v>
+        <v>5.079562621772997</v>
       </c>
       <c r="D2" t="n">
-        <v>43.6445759399962</v>
+        <v>21.44529685156733</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.64629308903066</v>
+        <v>15.49197877301467</v>
       </c>
       <c r="C3" t="n">
-        <v>36.57010198319369</v>
+        <v>34.42007451089317</v>
       </c>
       <c r="D3" t="n">
-        <v>65.09478153008477</v>
+        <v>56.72047361285948</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.4376227963826</v>
+        <v>22.29647211114931</v>
       </c>
       <c r="C4" t="n">
-        <v>63.45624461169684</v>
+        <v>61.06961594267284</v>
       </c>
       <c r="D4" t="n">
-        <v>59.72953032637594</v>
+        <v>48.77911643320702</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.4996528281994</v>
+        <v>21.20575041173111</v>
       </c>
       <c r="C5" t="n">
-        <v>98.66564427680447</v>
+        <v>63.61725123519332</v>
       </c>
       <c r="D5" t="n">
-        <v>39.5398887885403</v>
+        <v>31.48955761371645</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.901907345033331</v>
+        <v>11.99499345048753</v>
       </c>
       <c r="C6" t="n">
-        <v>77.645444181176</v>
+        <v>56.63407981488576</v>
       </c>
       <c r="D6" t="n">
-        <v>32.08056973167303</v>
+        <v>30.99377502307181</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.970588626601601</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>32.39865598784899</v>
+        <v>28.02693346083794</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>21.63281066307846</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>20.78359889890498</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.553926689373453</v>
+        <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>33.93999988351647</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>27.95035713990669</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.028219984773864</v>
+        <v>7.048311623001583</v>
       </c>
       <c r="C21" t="n">
-        <v>65.01103485915824</v>
+        <v>66.07792146563983</v>
       </c>
       <c r="D21" t="n">
-        <v>4.392637490483665</v>
+        <v>4.405194764375989</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.806235849364884</v>
+        <v>5.235660506748239</v>
       </c>
       <c r="C2" t="n">
-        <v>13.3262433374462</v>
+        <v>6.869288686614932</v>
       </c>
       <c r="D2" t="n">
-        <v>33.79175598017521</v>
+        <v>22.52325583083032</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.74370709592935</v>
+        <v>20.238728923048</v>
       </c>
       <c r="C3" t="n">
-        <v>49.50953672516665</v>
+        <v>25.15237618280328</v>
       </c>
       <c r="D3" t="n">
-        <v>84.90645020178539</v>
+        <v>61.03034603450297</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.72589676853267</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="C4" t="n">
-        <v>80.34132337703772</v>
+        <v>76.70394813280329</v>
       </c>
       <c r="D4" t="n">
-        <v>78.3631017529804</v>
+        <v>67.18295889701773</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.8564692131975</v>
+        <v>28.24979018970198</v>
       </c>
       <c r="C5" t="n">
-        <v>109.6121311791564</v>
+        <v>92.67698328089891</v>
       </c>
       <c r="D5" t="n">
-        <v>52.79348279587224</v>
+        <v>42.19060759000669</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.46921864936775</v>
+        <v>21.61513920440203</v>
       </c>
       <c r="C6" t="n">
-        <v>121.9625172985813</v>
+        <v>82.95866275655973</v>
       </c>
       <c r="D6" t="n">
-        <v>37.59504658642736</v>
+        <v>34.49566908412018</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>10.4801567428347</v>
       </c>
       <c r="C7" t="n">
-        <v>76.05599464800039</v>
+        <v>59.40751707938298</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>32.29459073119883</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>30.7296848906294</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.05772749256809</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>32.76190263842031</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6266,10 +6266,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.235975322517427</v>
+        <v>7.266094027196202</v>
       </c>
       <c r="C21" t="n">
-        <v>74.16874705580362</v>
+        <v>75.38572553216059</v>
       </c>
       <c r="D21" t="n">
-        <v>5.42698149188807</v>
+        <v>5.449570520397151</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.051271864799086</v>
+        <v>4.295146206079795</v>
       </c>
       <c r="C2" t="n">
-        <v>9.318749208710724</v>
+        <v>8.174031385558944</v>
       </c>
       <c r="D2" t="n">
-        <v>34.50352306575415</v>
+        <v>22.12073927208913</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.84893402673301</v>
+        <v>19.01645303126072</v>
       </c>
       <c r="C3" t="n">
-        <v>50.70236018582652</v>
+        <v>26.07521902479529</v>
       </c>
       <c r="D3" t="n">
-        <v>92.51990364821941</v>
+        <v>65.47275439621978</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.00140802052752</v>
+        <v>34.089225534562</v>
       </c>
       <c r="C4" t="n">
-        <v>104.2076100672777</v>
+        <v>68.80382435672921</v>
       </c>
       <c r="D4" t="n">
-        <v>99.82999705404117</v>
+        <v>81.18366290728149</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.64878066825368</v>
+        <v>34.95021827118646</v>
       </c>
       <c r="C5" t="n">
-        <v>130.1552018905209</v>
+        <v>120.215006385022</v>
       </c>
       <c r="D5" t="n">
-        <v>68.08420328951631</v>
+        <v>56.76956099807182</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.03652995370216</v>
+        <v>30.63151012020474</v>
       </c>
       <c r="C6" t="n">
-        <v>147.7638287138917</v>
+        <v>117.7763450876729</v>
       </c>
       <c r="D6" t="n">
-        <v>44.67933802027235</v>
+        <v>39.64788103600744</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.61233283000952</v>
+        <v>18.38518925743002</v>
       </c>
       <c r="C7" t="n">
-        <v>127.6183658227471</v>
+        <v>91.3869667975186</v>
       </c>
       <c r="D7" t="n">
-        <v>36.53083207502382</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.510369937488099</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>66.92574099850506</v>
+        <v>56.07742886657781</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>31.72812230584841</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
         <v>34.02246669067321</v>
@@ -6507,7 +6507,7 @@
         <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>25.41057582902019</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
         <v>35.53926689373453</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6636,7 +6636,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.427456048533822</v>
+        <v>7.470022839684361</v>
       </c>
       <c r="C21" t="n">
-        <v>82.63044853993877</v>
+        <v>84.03775694644906</v>
       </c>
       <c r="D21" t="n">
-        <v>6.499024042467094</v>
+        <v>6.536269984723816</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_58_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_58_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497630571843</v>
+        <v>10.84497635407622</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907184958262</v>
+        <v>37.78907201808421</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.98335134675681</v>
+        <v>5.959208564778139</v>
       </c>
       <c r="C2" t="n">
-        <v>6.71908128786517</v>
+        <v>9.600510799829559</v>
       </c>
       <c r="D2" t="n">
-        <v>21.07223272395354</v>
+        <v>26.48755306057894</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.63080610994097</v>
+        <v>17.61746255270901</v>
       </c>
       <c r="C3" t="n">
-        <v>29.08918447683299</v>
+        <v>35.29873870619407</v>
       </c>
       <c r="D3" t="n">
-        <v>67.46570223584081</v>
+        <v>93.86489800303754</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.08471770666826</v>
+        <v>38.7220929509027</v>
       </c>
       <c r="C4" t="n">
-        <v>66.8511281729823</v>
+        <v>74.0110141800543</v>
       </c>
       <c r="D4" t="n">
-        <v>94.09953570435253</v>
+        <v>98.27294519510572</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.04963683122264</v>
+        <v>47.1238898038469</v>
       </c>
       <c r="C5" t="n">
-        <v>122.4730261047896</v>
+        <v>103.9425381871311</v>
       </c>
       <c r="D5" t="n">
-        <v>70.71037839837653</v>
+        <v>60.96653243372694</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.68184129502858</v>
+        <v>41.25794727097221</v>
       </c>
       <c r="C6" t="n">
-        <v>154.6468618683661</v>
+        <v>99.13982841795567</v>
       </c>
       <c r="D6" t="n">
-        <v>47.81896717845365</v>
+        <v>42.42524529132167</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.18852092141116</v>
+        <v>27.60772719112455</v>
       </c>
       <c r="C7" t="n">
-        <v>129.8341703912322</v>
+        <v>92.28526594690442</v>
       </c>
       <c r="D7" t="n">
-        <v>38.98618308334508</v>
+        <v>38.5669768136317</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.26970288122739</v>
+        <v>14.52004854581032</v>
       </c>
       <c r="C8" t="n">
-        <v>88.8727109269425</v>
+        <v>58.83123117699011</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>50.03280825153018</v>
+        <v>35.72187196672443</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.659058415800023</v>
+        <v>7.705908486364204</v>
       </c>
       <c r="C21" t="n">
-        <v>92.86608329157528</v>
+        <v>96.32385607955256</v>
       </c>
       <c r="D21" t="n">
-        <v>7.659058415800023</v>
+        <v>8.669147047159729</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.241550992973721</v>
+        <v>7.291440199441061</v>
       </c>
       <c r="C2" t="n">
-        <v>12.04506258340412</v>
+        <v>8.010079518949725</v>
       </c>
       <c r="D2" t="n">
-        <v>24.74691438094935</v>
+        <v>24.64383087200343</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.47372647726148</v>
+        <v>18.71701998146544</v>
       </c>
       <c r="C3" t="n">
-        <v>27.42021337961341</v>
+        <v>36.14304173184632</v>
       </c>
       <c r="D3" t="n">
-        <v>67.88785374866693</v>
+        <v>92.79970174392975</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.96610616090365</v>
+        <v>35.85048091598077</v>
       </c>
       <c r="C4" t="n">
-        <v>68.85487523735006</v>
+        <v>80.2775097762617</v>
       </c>
       <c r="D4" t="n">
-        <v>102.8164735703599</v>
+        <v>118.1317377566102</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.07480241863456</v>
+        <v>52.57258956241671</v>
       </c>
       <c r="C5" t="n">
-        <v>121.4912784005428</v>
+        <v>119.8223073033232</v>
       </c>
       <c r="D5" t="n">
-        <v>85.48568134729102</v>
+        <v>79.98789420350889</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.2956956520901</v>
+        <v>51.4818678629985</v>
       </c>
       <c r="C6" t="n">
-        <v>173.5651401292021</v>
+        <v>129.3688219794192</v>
       </c>
       <c r="D6" t="n">
-        <v>56.51332484726341</v>
+        <v>50.27431818677493</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.99185258539232</v>
+        <v>37.60879105428681</v>
       </c>
       <c r="C7" t="n">
-        <v>171.6949107526119</v>
+        <v>117.1382090799124</v>
       </c>
       <c r="D7" t="n">
-        <v>43.29801900039708</v>
+        <v>41.98051358129786</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.9455872701057</v>
+        <v>21.86352137357647</v>
       </c>
       <c r="C8" t="n">
-        <v>127.5928403824367</v>
+        <v>88.28857104291565</v>
       </c>
       <c r="D8" t="n">
-        <v>37.55184968744049</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.31718662392973</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>76.87968097186344</v>
+        <v>53.58280795008665</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>44.4142661401257</v>
+        <v>36.15776794741003</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
         <v>35.36549755008285</v>
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>28.61794557879453</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.832809522194543</v>
+        <v>7.887998565558345</v>
       </c>
       <c r="C21" t="n">
-        <v>100.8474225982547</v>
+        <v>105.5019808143429</v>
       </c>
       <c r="D21" t="n">
-        <v>8.811910712468862</v>
+        <v>9.85999820694793</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.738135404873359</v>
+        <v>9.471901850573227</v>
       </c>
       <c r="C2" t="n">
-        <v>17.26108813606742</v>
+        <v>9.701630813366981</v>
       </c>
       <c r="D2" t="n">
-        <v>25.90243142884784</v>
+        <v>32.0422815712074</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.59644494029233</v>
+        <v>20.96522222419064</v>
       </c>
       <c r="C3" t="n">
-        <v>35.9368747139545</v>
+        <v>33.472687976295</v>
       </c>
       <c r="D3" t="n">
-        <v>70.24404823885929</v>
+        <v>90.60549562493813</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.47286790274425</v>
+        <v>34.9953786655818</v>
       </c>
       <c r="C4" t="n">
-        <v>67.78280674431252</v>
+        <v>84.65512278949821</v>
       </c>
       <c r="D4" t="n">
-        <v>109.3126981293611</v>
+        <v>133.4470019428604</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.13018120069989</v>
+        <v>52.81802648847841</v>
       </c>
       <c r="C5" t="n">
-        <v>123.4547738090364</v>
+        <v>130.7687942056752</v>
       </c>
       <c r="D5" t="n">
-        <v>99.03379966589702</v>
+        <v>97.9784208838317</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.49445065670446</v>
+        <v>59.57245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>180.4481732836765</v>
+        <v>154.6468618683661</v>
       </c>
       <c r="D6" t="n">
-        <v>66.45548384817086</v>
+        <v>61.22276858453534</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.01665831990574</v>
+        <v>48.02906118716245</v>
       </c>
       <c r="C7" t="n">
-        <v>203.8540203006247</v>
+        <v>148.0995864287441</v>
       </c>
       <c r="D7" t="n">
-        <v>48.44826745687584</v>
+        <v>45.63359678880023</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.12216298814988</v>
+        <v>29.70768553050848</v>
       </c>
       <c r="C8" t="n">
-        <v>170.1516033615359</v>
+        <v>116.7445282505095</v>
       </c>
       <c r="D8" t="n">
-        <v>39.63806355896497</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.64374875654542</v>
+        <v>15.42031119060464</v>
       </c>
       <c r="C9" t="n">
-        <v>109.7171781835107</v>
+        <v>77.32343093418301</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>36.60937189136354</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>63.06256378229386</v>
+        <v>48.25780840225197</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>40.33706792438868</v>
+        <v>36.60544490054656</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.990751787984228</v>
+        <v>8.053926003029924</v>
       </c>
       <c r="C21" t="n">
-        <v>107.8751491377871</v>
+        <v>113.7617047927977</v>
       </c>
       <c r="D21" t="n">
-        <v>9.988439734980284</v>
+        <v>11.07414825416615</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.961572970814132</v>
+        <v>8.515679586636832</v>
       </c>
       <c r="C2" t="n">
-        <v>12.01364665686822</v>
+        <v>6.596362824834318</v>
       </c>
       <c r="D2" t="n">
-        <v>21.39620946635499</v>
+        <v>26.32949168019521</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.63142800474672</v>
+        <v>24.68113728476482</v>
       </c>
       <c r="C3" t="n">
-        <v>54.48699758569798</v>
+        <v>51.08033305196155</v>
       </c>
       <c r="D3" t="n">
-        <v>76.97392875147118</v>
+        <v>99.26451037639499</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.11328620108265</v>
+        <v>25.37228766855457</v>
       </c>
       <c r="C4" t="n">
-        <v>98.05597895246717</v>
+        <v>112.4140391270768</v>
       </c>
       <c r="D4" t="n">
-        <v>106.9515949006475</v>
+        <v>122.3179099675186</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.11511082777092</v>
+        <v>33.55122779263475</v>
       </c>
       <c r="C5" t="n">
-        <v>107.820441618906</v>
+        <v>92.40700266223104</v>
       </c>
       <c r="D5" t="n">
-        <v>66.31705742187205</v>
+        <v>62.90548414961439</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.33087433852696</v>
+        <v>29.82647700272235</v>
       </c>
       <c r="C6" t="n">
-        <v>134.2392723401876</v>
+        <v>97.52976218299091</v>
       </c>
       <c r="D6" t="n">
-        <v>31.87931145230244</v>
+        <v>30.02773528209295</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.62473569726624</v>
+        <v>19.64280806657018</v>
       </c>
       <c r="C7" t="n">
-        <v>119.6534466981928</v>
+        <v>82.10454225386499</v>
       </c>
       <c r="D7" t="n">
-        <v>27.84727363096077</v>
+        <v>28.62579956042849</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>80.86164966028853</v>
+        <v>56.99536297004857</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>48.14687091167205</v>
+        <v>36.83124687252333</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>27.84531013555227</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>28.61303684027329</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>26.4698816019025</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.169482499936204</v>
+        <v>5.132576997802325</v>
       </c>
       <c r="C2" t="n">
-        <v>5.517422097867075</v>
+        <v>3.632466505713198</v>
       </c>
       <c r="D2" t="n">
-        <v>15.20432669567035</v>
+        <v>18.14858806070654</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.63419332141021</v>
+        <v>27.50366193447439</v>
       </c>
       <c r="C3" t="n">
-        <v>51.74792149084938</v>
+        <v>39.21591204613884</v>
       </c>
       <c r="D3" t="n">
-        <v>77.35681035612743</v>
+        <v>97.94896845270426</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.04344324536089</v>
+        <v>34.79117514309847</v>
       </c>
       <c r="C4" t="n">
-        <v>118.5146193612665</v>
+        <v>122.7007915721749</v>
       </c>
       <c r="D4" t="n">
-        <v>118.1445004767654</v>
+        <v>141.7938209243668</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.57577148524092</v>
+        <v>37.35550014659114</v>
       </c>
       <c r="C5" t="n">
-        <v>143.3106211274282</v>
+        <v>146.0104273141069</v>
       </c>
       <c r="D5" t="n">
-        <v>83.59581701661591</v>
+        <v>83.6939917870406</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.08056973167303</v>
+        <v>35.50196048097316</v>
       </c>
       <c r="C6" t="n">
-        <v>156.7399479738203</v>
+        <v>121.1574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>39.04410619789565</v>
+        <v>37.55479493055324</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.36711688812607</v>
+        <v>18.50496247734813</v>
       </c>
       <c r="C7" t="n">
-        <v>149.3572052378842</v>
+        <v>106.5981657271187</v>
       </c>
       <c r="D7" t="n">
-        <v>30.3625112492411</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>106.56380455747</v>
+        <v>75.10369937488099</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>52.47343304428775</v>
+        <v>41.82343394861835</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
         <v>28.20561154301086</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.950552761889165</v>
+        <v>4.423755155336128</v>
       </c>
       <c r="C2" t="n">
-        <v>6.684720118216532</v>
+        <v>7.236462328003239</v>
       </c>
       <c r="D2" t="n">
-        <v>14.99423268696153</v>
+        <v>18.30959468420301</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.57466656434965</v>
+        <v>22.64891953697392</v>
       </c>
       <c r="C3" t="n">
-        <v>36.09395434663399</v>
+        <v>26.00158794697677</v>
       </c>
       <c r="D3" t="n">
-        <v>71.9768329368549</v>
+        <v>90.3846023914826</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.91429451675682</v>
+        <v>43.04865508351838</v>
       </c>
       <c r="C4" t="n">
-        <v>123.7345719047467</v>
+        <v>109.9891222975871</v>
       </c>
       <c r="D4" t="n">
-        <v>128.0866594776729</v>
+        <v>155.8966266958723</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.85266539556753</v>
+        <v>44.30136515413732</v>
       </c>
       <c r="C5" t="n">
-        <v>180.6661212740193</v>
+        <v>186.679325962531</v>
       </c>
       <c r="D5" t="n">
-        <v>103.1080526385213</v>
+        <v>110.1766361090983</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.95731148929444</v>
+        <v>42.66675522656639</v>
       </c>
       <c r="C6" t="n">
-        <v>189.0620276407381</v>
+        <v>172.1965838294821</v>
       </c>
       <c r="D6" t="n">
-        <v>52.60891422747383</v>
+        <v>51.40136455125026</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.63146906247572</v>
+        <v>27.72750041104266</v>
       </c>
       <c r="C7" t="n">
-        <v>186.0676971427852</v>
+        <v>139.356141374722</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>34.19525428662065</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.10004045484194</v>
+        <v>13.10142311317368</v>
       </c>
       <c r="C8" t="n">
-        <v>147.3701478844887</v>
+        <v>105.3120762345553</v>
       </c>
       <c r="D8" t="n">
-        <v>29.29044275620359</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>85.19999276535516</v>
+        <v>63.78905708343648</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>45.26838664282043</v>
+        <v>39.85895679242051</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
         <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.364048471826319</v>
+        <v>2.635992585902686</v>
       </c>
       <c r="C2" t="n">
-        <v>3.204424506661589</v>
+        <v>3.39488356128547</v>
       </c>
       <c r="D2" t="n">
-        <v>10.44383207777757</v>
+        <v>12.79315433404019</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.34886459237289</v>
+        <v>21.91751749731004</v>
       </c>
       <c r="C3" t="n">
-        <v>34.17463758483147</v>
+        <v>28.62776305583699</v>
       </c>
       <c r="D3" t="n">
-        <v>70.67110849020665</v>
+        <v>88.48001184524378</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.44956799974958</v>
+        <v>47.45179353706533</v>
       </c>
       <c r="C4" t="n">
-        <v>123.568656542729</v>
+        <v>104.4245763099162</v>
       </c>
       <c r="D4" t="n">
-        <v>135.9484950932813</v>
+        <v>166.0174637789526</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.54618018539328</v>
+        <v>46.19122948481243</v>
       </c>
       <c r="C5" t="n">
-        <v>222.3658550119026</v>
+        <v>221.0895829963818</v>
       </c>
       <c r="D5" t="n">
-        <v>108.5322087044849</v>
+        <v>116.7052583423396</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.99377502307181</v>
+        <v>34.5359207399943</v>
       </c>
       <c r="C6" t="n">
-        <v>225.3287695833195</v>
+        <v>203.5928754112951</v>
       </c>
       <c r="D6" t="n">
-        <v>51.44161620712438</v>
+        <v>50.4353248102714</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.964919124554372</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>192.8947706781175</v>
+        <v>142.590018312511</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>34.31502750653876</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>106.0631132283042</v>
+        <v>78.94233289848603</v>
       </c>
       <c r="D8" t="n">
-        <v>31.12631096314512</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
         <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
         <v>22.92282714645877</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.589850443803086</v>
+        <v>2.934443887993716</v>
       </c>
       <c r="C2" t="n">
-        <v>6.889905388404116</v>
+        <v>4.300054944601029</v>
       </c>
       <c r="D2" t="n">
-        <v>10.94648690235194</v>
+        <v>21.78792680034946</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.47448724078747</v>
+        <v>15.7128720064702</v>
       </c>
       <c r="C3" t="n">
-        <v>23.33614292994668</v>
+        <v>20.80323385298991</v>
       </c>
       <c r="D3" t="n">
-        <v>63.67124735892688</v>
+        <v>80.04679906576369</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.29266829351933</v>
+        <v>45.20555478974863</v>
       </c>
       <c r="C4" t="n">
-        <v>106.185831691335</v>
+        <v>89.13483756397642</v>
       </c>
       <c r="D4" t="n">
-        <v>139.1519378522387</v>
+        <v>170.8034838371558</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.44924920458011</v>
+        <v>56.64684253504097</v>
       </c>
       <c r="C5" t="n">
-        <v>224.3293504203962</v>
+        <v>209.6522222419064</v>
       </c>
       <c r="D5" t="n">
-        <v>127.2345024703866</v>
+        <v>142.3043297305752</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.21140421824511</v>
+        <v>44.96109961139118</v>
       </c>
       <c r="C6" t="n">
-        <v>285.2232335240089</v>
+        <v>269.3640811096059</v>
       </c>
       <c r="D6" t="n">
-        <v>68.26680836250623</v>
+        <v>68.70957657712154</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.94791061841269</v>
+        <v>19.10382857693868</v>
       </c>
       <c r="C7" t="n">
-        <v>249.0684108197115</v>
+        <v>208.1658562176767</v>
       </c>
       <c r="D7" t="n">
-        <v>38.50709020367265</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>165.4784842893211</v>
+        <v>122.669375645639</v>
       </c>
       <c r="D8" t="n">
-        <v>32.7952820603647</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>68.89218165011141</v>
+        <v>54.58124536530566</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
         <v>23.63361248433346</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.748492661263569</v>
+        <v>2.280599916965341</v>
       </c>
       <c r="C2" t="n">
-        <v>3.657991946023615</v>
+        <v>2.934443887993716</v>
       </c>
       <c r="D2" t="n">
-        <v>8.598146393793566</v>
+        <v>15.80024755214817</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.67298020349457</v>
+        <v>13.47448724078747</v>
       </c>
       <c r="C3" t="n">
-        <v>25.06401888942107</v>
+        <v>19.14898897133403</v>
       </c>
       <c r="D3" t="n">
-        <v>59.30737881354982</v>
+        <v>79.92408060273283</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.74463209037137</v>
+        <v>40.48334833232148</v>
       </c>
       <c r="C4" t="n">
-        <v>89.10931212366599</v>
+        <v>75.70845596069702</v>
       </c>
       <c r="D4" t="n">
-        <v>139.5475821770501</v>
+        <v>171.9010777705037</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.20443417332415</v>
+        <v>62.34097921967247</v>
       </c>
       <c r="C5" t="n">
-        <v>221.3104762298373</v>
+        <v>199.7365704290136</v>
       </c>
       <c r="D5" t="n">
-        <v>140.6108149407494</v>
+        <v>158.994040702771</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.89317909334891</v>
+        <v>52.76992085097032</v>
       </c>
       <c r="C6" t="n">
-        <v>321.1679622195974</v>
+        <v>302.9339621086213</v>
       </c>
       <c r="D6" t="n">
-        <v>79.57752366313373</v>
+        <v>84.1259607769092</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.15131231964102</v>
+        <v>17.18745705824891</v>
       </c>
       <c r="C7" t="n">
-        <v>303.0861330027795</v>
+        <v>267.6332599070187</v>
       </c>
       <c r="D7" t="n">
-        <v>42.99858595060179</v>
+        <v>43.95677170994669</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>211.2917409079985</v>
+        <v>160.0543282233575</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>75.43749359432489</v>
+        <v>62.23593221531803</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.067961575771282</v>
+        <v>3.536255230697011</v>
       </c>
       <c r="C2" t="n">
-        <v>13.12105806725862</v>
+        <v>9.837111996553039</v>
       </c>
       <c r="D2" t="n">
-        <v>8.330129270534187</v>
+        <v>12.83046074680156</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.978082755337082</v>
+        <v>10.74522862298134</v>
       </c>
       <c r="C3" t="n">
-        <v>20.00310947402876</v>
+        <v>15.63924092865169</v>
       </c>
       <c r="D3" t="n">
-        <v>54.11884219660542</v>
+        <v>74.69627407761857</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.58849314766712</v>
+        <v>33.55319128804324</v>
       </c>
       <c r="C4" t="n">
-        <v>77.36760958087413</v>
+        <v>62.70324412253954</v>
       </c>
       <c r="D4" t="n">
-        <v>135.9229696529709</v>
+        <v>171.8372641697277</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.44357970253288</v>
+        <v>62.19371706403545</v>
       </c>
       <c r="C5" t="n">
-        <v>197.0367642423349</v>
+        <v>173.7447999590793</v>
       </c>
       <c r="D5" t="n">
-        <v>153.4962535589888</v>
+        <v>177.2054606165493</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.34602682691394</v>
+        <v>63.4366096576119</v>
       </c>
       <c r="C6" t="n">
-        <v>334.1692470669379</v>
+        <v>312.7956177977806</v>
       </c>
       <c r="D6" t="n">
-        <v>97.36875555949442</v>
+        <v>105.0568218314512</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.02693346083794</v>
+        <v>32.21899615797182</v>
       </c>
       <c r="C7" t="n">
-        <v>369.2608370075358</v>
+        <v>333.867850521734</v>
       </c>
       <c r="D7" t="n">
-        <v>51.38271134486956</v>
+        <v>52.99964981376406</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>281.4719755460818</v>
+        <v>232.988365171853</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>36.88426124855267</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>140.55780056472</v>
+        <v>111.492178032789</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>50.82016991033614</v>
+        <v>45.98015372839937</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.458517235612265</v>
+        <v>5.115887286830128</v>
       </c>
       <c r="C2" t="n">
-        <v>11.54535300194249</v>
+        <v>4.442408361716817</v>
       </c>
       <c r="D2" t="n">
-        <v>7.127488332831843</v>
+        <v>7.319910882864218</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.242311756499715</v>
+        <v>2.558434517267188</v>
       </c>
       <c r="C2" t="n">
-        <v>7.662540831646355</v>
+        <v>5.665666001208343</v>
       </c>
       <c r="D2" t="n">
-        <v>6.196791509205867</v>
+        <v>9.545532928391737</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.40438224315845</v>
+        <v>14.74585051778709</v>
       </c>
       <c r="C3" t="n">
-        <v>31.6417285078747</v>
+        <v>24.52896639060656</v>
       </c>
       <c r="D3" t="n">
-        <v>58.30108741669683</v>
+        <v>79.73754853892594</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.3219407981975</v>
+        <v>47.00509833163304</v>
       </c>
       <c r="C4" t="n">
-        <v>112.1970728844382</v>
+        <v>92.70839920743479</v>
       </c>
       <c r="D4" t="n">
-        <v>139.2029887328595</v>
+        <v>175.525690294583</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.63681976935347</v>
+        <v>36.88916998707391</v>
       </c>
       <c r="C5" t="n">
-        <v>288.58473766335</v>
+        <v>263.1329284307514</v>
       </c>
       <c r="D5" t="n">
-        <v>140.1690284738384</v>
+        <v>158.9694970101648</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.38871533761951</v>
+        <v>20.00507296943726</v>
       </c>
       <c r="C6" t="n">
-        <v>302.1691806470131</v>
+        <v>278.1389420901639</v>
       </c>
       <c r="D6" t="n">
-        <v>76.1963845697077</v>
+        <v>81.8316163920844</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>197.9252459146782</v>
+        <v>163.8497648479756</v>
       </c>
       <c r="D7" t="n">
-        <v>32.15910954801276</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>103.5596565824748</v>
+        <v>82.11337798320321</v>
       </c>
       <c r="D8" t="n">
-        <v>24.11663235482289</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>38.71718421238145</v>
+        <v>35.05624702324509</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>22.06477965294707</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.284167054883833</v>
+        <v>5.711808143307943</v>
       </c>
       <c r="C2" t="n">
-        <v>5.033420479673397</v>
+        <v>5.114905539125882</v>
       </c>
       <c r="D2" t="n">
-        <v>19.81068692399639</v>
+        <v>10.08745766113598</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.59934912567607</v>
+        <v>10.87285582453342</v>
       </c>
       <c r="C3" t="n">
-        <v>29.09409321535422</v>
+        <v>11.36863841517807</v>
       </c>
       <c r="D3" t="n">
-        <v>9.125344910974103</v>
+        <v>9.576948854927634</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3978592400621</v>
+        <v>13.39910580118038</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14173366856043</v>
+        <v>70.14825978265024</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576218734124953</v>
+        <v>1.576365388374163</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.928373475318988</v>
+        <v>5.060909415392308</v>
       </c>
       <c r="C2" t="n">
-        <v>5.230751768227005</v>
+        <v>6.429465715112362</v>
       </c>
       <c r="D2" t="n">
-        <v>26.63874220703295</v>
+        <v>16.02703127182918</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.66164119940012</v>
+        <v>16.1890196430299</v>
       </c>
       <c r="C3" t="n">
-        <v>23.17415455874596</v>
+        <v>16.83206438931157</v>
       </c>
       <c r="D3" t="n">
-        <v>23.55703616340222</v>
+        <v>15.73250696055514</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.54124608467625</v>
+        <v>12.7116692745877</v>
       </c>
       <c r="C4" t="n">
-        <v>44.8737240657132</v>
+        <v>18.14858806070654</v>
       </c>
       <c r="D4" t="n">
-        <v>19.84602984134927</v>
+        <v>20.08852152429823</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43868517439593</v>
+        <v>15.4454376343458</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13161202557728</v>
+        <v>86.169283644245</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250249510399143</v>
+        <v>3.251671080914905</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.710425484976196</v>
+        <v>4.485605260703677</v>
       </c>
       <c r="C2" t="n">
-        <v>12.11967540892687</v>
+        <v>5.027529993447916</v>
       </c>
       <c r="D2" t="n">
-        <v>27.23269956810227</v>
+        <v>19.23047403078652</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.33275571847744</v>
+        <v>17.15604113171301</v>
       </c>
       <c r="C3" t="n">
-        <v>21.47573103039898</v>
+        <v>21.79479903427919</v>
       </c>
       <c r="D3" t="n">
-        <v>39.40244410994573</v>
+        <v>24.90203051822035</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.28294862746811</v>
+        <v>23.20262524216912</v>
       </c>
       <c r="C4" t="n">
-        <v>52.07189823325082</v>
+        <v>32.09824119034946</v>
       </c>
       <c r="D4" t="n">
-        <v>27.18459393059418</v>
+        <v>23.27920156310037</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.95277829920492</v>
+        <v>11.51099183229385</v>
       </c>
       <c r="C5" t="n">
-        <v>49.57825906446394</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D5" t="n">
-        <v>29.82058651649687</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72743897952156</v>
+        <v>16.74466133130946</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0373777750815</v>
+        <v>102.1424341209877</v>
       </c>
       <c r="D21" t="n">
-        <v>4.18185974488039</v>
+        <v>5.023398399392836</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.308309836862503</v>
+        <v>6.802529842726149</v>
       </c>
       <c r="C2" t="n">
-        <v>9.602474295238052</v>
+        <v>3.932881303212722</v>
       </c>
       <c r="D2" t="n">
-        <v>26.80760281216341</v>
+        <v>27.5164246546296</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.64062358698343</v>
+        <v>16.17920216598743</v>
       </c>
       <c r="C3" t="n">
-        <v>35.9368747139545</v>
+        <v>20.45962215650353</v>
       </c>
       <c r="D3" t="n">
-        <v>51.33558745506572</v>
+        <v>33.9782880439821</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.50740899884213</v>
+        <v>28.52467954689108</v>
       </c>
       <c r="C4" t="n">
-        <v>52.46754255806228</v>
+        <v>44.8737240657132</v>
       </c>
       <c r="D4" t="n">
-        <v>40.0749412873548</v>
+        <v>29.9030533236536</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.93639168786899</v>
+        <v>23.4392264388926</v>
       </c>
       <c r="C5" t="n">
-        <v>74.73554398578845</v>
+        <v>42.36241343824987</v>
       </c>
       <c r="D5" t="n">
-        <v>32.49584901056943</v>
+        <v>31.80862561759666</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.94845039776043</v>
+        <v>10.74719211838983</v>
       </c>
       <c r="C6" t="n">
-        <v>46.57116584635595</v>
+        <v>23.82898027747859</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>37.91705983342032</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5591,7 +5591,7 @@
         <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04469539760044</v>
+        <v>18.07932865166267</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7201556891076</v>
+        <v>117.9460964417993</v>
       </c>
       <c r="D21" t="n">
-        <v>6.014898465866811</v>
+        <v>6.887363295871493</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.685701865920779</v>
+        <v>6.893832379221102</v>
       </c>
       <c r="C2" t="n">
-        <v>5.079562621772997</v>
+        <v>12.43088943117311</v>
       </c>
       <c r="D2" t="n">
-        <v>21.44529685156733</v>
+        <v>39.66751599009237</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.49197877301467</v>
+        <v>18.13778883595982</v>
       </c>
       <c r="C3" t="n">
-        <v>34.42007451089317</v>
+        <v>16.4050041379642</v>
       </c>
       <c r="D3" t="n">
-        <v>56.72047361285948</v>
+        <v>44.52716712611409</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.29647211114931</v>
+        <v>21.90082778633785</v>
       </c>
       <c r="C4" t="n">
-        <v>61.06961594267284</v>
+        <v>40.62373825402877</v>
       </c>
       <c r="D4" t="n">
-        <v>48.77911643320702</v>
+        <v>34.34447993766616</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.20575041173111</v>
+        <v>20.64124548178919</v>
       </c>
       <c r="C5" t="n">
-        <v>63.61725123519332</v>
+        <v>47.68839473378882</v>
       </c>
       <c r="D5" t="n">
-        <v>31.48955761371645</v>
+        <v>28.78975142703772</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.99499345048753</v>
+        <v>11.7132318593687</v>
       </c>
       <c r="C6" t="n">
-        <v>56.63407981488576</v>
+        <v>31.83905979642831</v>
       </c>
       <c r="D6" t="n">
-        <v>30.99377502307181</v>
+        <v>30.39000018496002</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>28.02693346083794</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.048311623001583</v>
+        <v>7.069705925700821</v>
       </c>
       <c r="C21" t="n">
-        <v>66.07792146563983</v>
+        <v>67.1622062941578</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405194764375989</v>
+        <v>5.302279444275616</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.235660506748239</v>
+        <v>5.406484607287184</v>
       </c>
       <c r="C2" t="n">
-        <v>6.869288686614932</v>
+        <v>6.515859513086081</v>
       </c>
       <c r="D2" t="n">
-        <v>22.52325583083032</v>
+        <v>42.39088412167303</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.238728923048</v>
+        <v>22.15313694632928</v>
       </c>
       <c r="C3" t="n">
-        <v>25.15237618280328</v>
+        <v>37.48803608666446</v>
       </c>
       <c r="D3" t="n">
-        <v>61.03034603450297</v>
+        <v>68.24619166071703</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.33774657245668</v>
+        <v>30.24764676784423</v>
       </c>
       <c r="C4" t="n">
-        <v>76.70394813280329</v>
+        <v>41.01938257884023</v>
       </c>
       <c r="D4" t="n">
-        <v>67.18295889701773</v>
+        <v>50.48932093400496</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.24979018970198</v>
+        <v>28.17615911188346</v>
       </c>
       <c r="C5" t="n">
-        <v>92.67698328089891</v>
+        <v>64.79534848028949</v>
       </c>
       <c r="D5" t="n">
-        <v>42.19060759000669</v>
+        <v>35.41654843070369</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.61513920440203</v>
+        <v>21.1321193339126</v>
       </c>
       <c r="C6" t="n">
-        <v>82.95866275655973</v>
+        <v>58.12339108222817</v>
       </c>
       <c r="D6" t="n">
-        <v>34.49566908412018</v>
+        <v>32.88560284915541</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.4801567428347</v>
+        <v>10.54004335279375</v>
       </c>
       <c r="C7" t="n">
-        <v>59.40751707938298</v>
+        <v>34.49468733641593</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>33.77604801690726</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>22.19731559302038</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -6168,7 +6168,7 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
         <v>31.39530983410874</v>
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.266094027196202</v>
+        <v>7.295678699223436</v>
       </c>
       <c r="C21" t="n">
-        <v>75.38572553216059</v>
+        <v>77.516586179249</v>
       </c>
       <c r="D21" t="n">
-        <v>5.449570520397151</v>
+        <v>6.383718861820507</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.295146206079795</v>
+        <v>4.513094196422587</v>
       </c>
       <c r="C2" t="n">
-        <v>8.174031385558944</v>
+        <v>10.14930776650353</v>
       </c>
       <c r="D2" t="n">
-        <v>22.12073927208913</v>
+        <v>35.18485597250144</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.01645303126072</v>
+        <v>20.24854640009046</v>
       </c>
       <c r="C3" t="n">
-        <v>26.07521902479529</v>
+        <v>30.03166227290993</v>
       </c>
       <c r="D3" t="n">
-        <v>65.47275439621978</v>
+        <v>86.32507563442203</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.089225534562</v>
+        <v>37.93080430127976</v>
       </c>
       <c r="C4" t="n">
-        <v>68.80382435672921</v>
+        <v>72.6709285637574</v>
       </c>
       <c r="D4" t="n">
-        <v>81.18366290728149</v>
+        <v>72.8368439257751</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.95021827118646</v>
+        <v>37.57639338004667</v>
       </c>
       <c r="C5" t="n">
-        <v>120.215006385022</v>
+        <v>71.27488332831845</v>
       </c>
       <c r="D5" t="n">
-        <v>56.76956099807182</v>
+        <v>46.16668579220627</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.63151012020474</v>
+        <v>30.79251674370121</v>
       </c>
       <c r="C6" t="n">
-        <v>117.7763450876729</v>
+        <v>83.32092765942681</v>
       </c>
       <c r="D6" t="n">
-        <v>39.64788103600744</v>
+        <v>36.99127174831558</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.38518925743002</v>
+        <v>18.56484908730718</v>
       </c>
       <c r="C7" t="n">
-        <v>91.3869667975186</v>
+        <v>61.98264130762237</v>
       </c>
       <c r="D7" t="n">
-        <v>36.17151241526948</v>
+        <v>35.75230614555609</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>56.07742886657781</v>
+        <v>35.13184159647211</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>30.84062238120929</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.470022839684361</v>
+        <v>7.508247247797547</v>
       </c>
       <c r="C21" t="n">
-        <v>84.03775694644906</v>
+        <v>87.28337425564648</v>
       </c>
       <c r="D21" t="n">
-        <v>6.536269984723816</v>
+        <v>7.508247247797547</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_58_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_58_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497635407622</v>
+        <v>10.84497636923998</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907201808421</v>
+        <v>37.78907207092199</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.959208564778139</v>
+        <v>1.847649179392497</v>
       </c>
       <c r="C2" t="n">
-        <v>9.600510799829559</v>
+        <v>2.599667920845554</v>
       </c>
       <c r="D2" t="n">
-        <v>26.48755306057894</v>
+        <v>12.74504869653209</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.61746255270901</v>
+        <v>13.34686003923539</v>
       </c>
       <c r="C3" t="n">
-        <v>35.29873870619407</v>
+        <v>44.82660017590936</v>
       </c>
       <c r="D3" t="n">
-        <v>93.86489800303754</v>
+        <v>55.32148313430777</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.7220929509027</v>
+        <v>21.73491242432013</v>
       </c>
       <c r="C4" t="n">
-        <v>74.0110141800543</v>
+        <v>151.7359799252743</v>
       </c>
       <c r="D4" t="n">
-        <v>98.27294519510572</v>
+        <v>69.11012964045422</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.1238898038469</v>
+        <v>23.14470212761856</v>
       </c>
       <c r="C5" t="n">
-        <v>103.9425381871311</v>
+        <v>145.6668156176205</v>
       </c>
       <c r="D5" t="n">
-        <v>60.96653243372694</v>
+        <v>45.4794623992335</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.25794727097221</v>
+        <v>14.93336432929824</v>
       </c>
       <c r="C6" t="n">
-        <v>99.13982841795567</v>
+        <v>80.82532499523143</v>
       </c>
       <c r="D6" t="n">
-        <v>42.42524529132167</v>
+        <v>29.74597369097411</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.60772719112455</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>92.28526594690442</v>
+        <v>43.17824578047897</v>
       </c>
       <c r="D7" t="n">
-        <v>38.5669768136317</v>
+        <v>28.86534600026472</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.52004854581032</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>58.83123117699011</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
+        <v>30.84062238120929</v>
+      </c>
+      <c r="D9" t="n">
         <v>35.72187196672443</v>
-      </c>
-      <c r="D9" t="n">
-        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>37.29659528433633</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.705908486364204</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>96.32385607955256</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.669147047159729</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.291440199441061</v>
+        <v>1.699405276051229</v>
       </c>
       <c r="C2" t="n">
-        <v>8.010079518949725</v>
+        <v>3.603014074585794</v>
       </c>
       <c r="D2" t="n">
-        <v>24.64383087200343</v>
+        <v>21.12622884768711</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.71701998146544</v>
+        <v>9.650579932746147</v>
       </c>
       <c r="C3" t="n">
-        <v>36.14304173184632</v>
+        <v>25.18673735245192</v>
       </c>
       <c r="D3" t="n">
-        <v>92.79970174392975</v>
+        <v>52.70021676396878</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.85048091598077</v>
+        <v>24.04496477241288</v>
       </c>
       <c r="C4" t="n">
-        <v>80.2775097762617</v>
+        <v>130.0010675009542</v>
       </c>
       <c r="D4" t="n">
-        <v>118.1317377566102</v>
+        <v>80.63486594060753</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.57258956241671</v>
+        <v>27.9798095710341</v>
       </c>
       <c r="C5" t="n">
-        <v>119.8223073033232</v>
+        <v>218.3652331170968</v>
       </c>
       <c r="D5" t="n">
-        <v>79.98789420350889</v>
+        <v>59.19938656608268</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.4818678629985</v>
+        <v>22.62143060125501</v>
       </c>
       <c r="C6" t="n">
-        <v>129.3688219794192</v>
+        <v>156.6191930061979</v>
       </c>
       <c r="D6" t="n">
-        <v>50.27431818677493</v>
+        <v>36.91076843656734</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.60879105428681</v>
+        <v>11.19879606234337</v>
       </c>
       <c r="C7" t="n">
-        <v>117.1382090799124</v>
+        <v>79.05032514595315</v>
       </c>
       <c r="D7" t="n">
-        <v>41.98051358129786</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.86352137357647</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>88.28857104291565</v>
+        <v>43.0594543082651</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>53.58280795008665</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>36.15776794741003</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>37.72365553568369</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>36.42283982755666</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.13585070274711</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.887998565558345</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105.5019808143429</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.85999820694793</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.471901850573227</v>
+        <v>0.9297150759217294</v>
       </c>
       <c r="C2" t="n">
-        <v>9.701630813366981</v>
+        <v>1.595340019401067</v>
       </c>
       <c r="D2" t="n">
-        <v>32.0422815712074</v>
+        <v>14.37965862410303</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.96522222419064</v>
+        <v>8.997717709422018</v>
       </c>
       <c r="C3" t="n">
-        <v>33.472687976295</v>
+        <v>21.61808444751476</v>
       </c>
       <c r="D3" t="n">
-        <v>90.60549562493813</v>
+        <v>57.70222131710628</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.9953786655818</v>
+        <v>26.39330528097125</v>
       </c>
       <c r="C4" t="n">
-        <v>84.65512278949821</v>
+        <v>116.2300924534841</v>
       </c>
       <c r="D4" t="n">
-        <v>133.4470019428604</v>
+        <v>87.99895547016284</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.81802648847841</v>
+        <v>28.20070280448963</v>
       </c>
       <c r="C5" t="n">
-        <v>130.7687942056752</v>
+        <v>255.0335098707152</v>
       </c>
       <c r="D5" t="n">
-        <v>97.9784208838317</v>
+        <v>66.46431957750907</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.57245069369646</v>
+        <v>16.7446888436336</v>
       </c>
       <c r="C6" t="n">
-        <v>154.6468618683661</v>
+        <v>196.4280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>61.22276858453534</v>
+        <v>37.39378830705677</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.02906118716245</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>148.0995864287441</v>
+        <v>74.97803566873739</v>
       </c>
       <c r="D7" t="n">
-        <v>45.63359678880023</v>
+        <v>32.57831581772616</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.70768553050848</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>116.7445282505095</v>
+        <v>39.72151211382594</v>
       </c>
       <c r="D8" t="n">
-        <v>40.72289477215769</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.42031119060464</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>77.32343093418301</v>
+        <v>26.07031028627404</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>48.25780840225197</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>36.58482819875739</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>36.60544490054656</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>39.05883241345935</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.053926003029924</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113.7617047927977</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.07414825416615</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.515679586636832</v>
+        <v>0.6744606728175587</v>
       </c>
       <c r="C2" t="n">
-        <v>6.596362824834318</v>
+        <v>4.985314842165304</v>
       </c>
       <c r="D2" t="n">
-        <v>26.32949168019521</v>
+        <v>11.93608858823272</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.68113728476482</v>
+        <v>6.081927027808991</v>
       </c>
       <c r="C3" t="n">
-        <v>51.08033305196155</v>
+        <v>13.19959788359837</v>
       </c>
       <c r="D3" t="n">
-        <v>99.26451037639499</v>
+        <v>55.77308707826131</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.37228766855457</v>
+        <v>22.30923483130452</v>
       </c>
       <c r="C4" t="n">
-        <v>112.4140391270768</v>
+        <v>84.38710566623882</v>
       </c>
       <c r="D4" t="n">
-        <v>122.3179099675186</v>
+        <v>96.88180869818798</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.55122779263475</v>
+        <v>33.62485887045326</v>
       </c>
       <c r="C5" t="n">
-        <v>92.40700266223104</v>
+        <v>237.0429831903924</v>
       </c>
       <c r="D5" t="n">
-        <v>62.90548414961439</v>
+        <v>80.20878743696441</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.82647700272235</v>
+        <v>25.47929816831747</v>
       </c>
       <c r="C6" t="n">
-        <v>97.52976218299091</v>
+        <v>298.42577665072</v>
       </c>
       <c r="D6" t="n">
-        <v>30.02773528209295</v>
+        <v>47.17494068446774</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.64280806657018</v>
+        <v>9.701630813366979</v>
       </c>
       <c r="C7" t="n">
-        <v>82.10454225386499</v>
+        <v>167.9220543251914</v>
       </c>
       <c r="D7" t="n">
-        <v>28.62579956042849</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>56.99536297004857</v>
+        <v>65.17332134642452</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>37.30150402285756</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>36.83124687252333</v>
+        <v>35.94374694788421</v>
       </c>
       <c r="D9" t="n">
-        <v>27.84531013555227</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>28.61303684027329</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
+        <v>21.20280516861837</v>
+      </c>
+      <c r="D14" t="n">
         <v>20.89551813718911</v>
-      </c>
-      <c r="D14" t="n">
-        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>46.74984392852887</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.132576997802325</v>
+        <v>0.4781111319681966</v>
       </c>
       <c r="C2" t="n">
-        <v>3.632466505713198</v>
+        <v>3.662900684544849</v>
       </c>
       <c r="D2" t="n">
-        <v>18.14858806070654</v>
+        <v>9.583821088857363</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.50366193447439</v>
+        <v>4.496404485450391</v>
       </c>
       <c r="C3" t="n">
-        <v>39.21591204613884</v>
+        <v>16.40991287648544</v>
       </c>
       <c r="D3" t="n">
-        <v>97.94896845270426</v>
+        <v>53.14691196940109</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.79117514309847</v>
+        <v>18.69738502738051</v>
       </c>
       <c r="C4" t="n">
-        <v>122.7007915721749</v>
+        <v>62.9457358054885</v>
       </c>
       <c r="D4" t="n">
-        <v>141.7938209243668</v>
+        <v>101.7954559579433</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.35550014659114</v>
+        <v>35.53926689373454</v>
       </c>
       <c r="C5" t="n">
-        <v>146.0104273141069</v>
+        <v>211.7875234986432</v>
       </c>
       <c r="D5" t="n">
-        <v>83.6939917870406</v>
+        <v>92.52972112526189</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.50196048097316</v>
+        <v>30.83276839957533</v>
       </c>
       <c r="C6" t="n">
-        <v>121.1574841810989</v>
+        <v>341.1730351890346</v>
       </c>
       <c r="D6" t="n">
-        <v>37.55479493055324</v>
+        <v>56.07055663264809</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.50496247734813</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C7" t="n">
-        <v>106.5981657271187</v>
+        <v>255.1169584255761</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>38.92629647338602</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>75.10369937488099</v>
+        <v>103.4762080276138</v>
       </c>
       <c r="D8" t="n">
-        <v>28.20561154301086</v>
+        <v>39.47116644924301</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>41.82343394861835</v>
+        <v>44.92968368485526</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.423755155336128</v>
+        <v>0.7284567965511333</v>
       </c>
       <c r="C2" t="n">
-        <v>7.236462328003239</v>
+        <v>4.274529504290612</v>
       </c>
       <c r="D2" t="n">
-        <v>18.30959468420301</v>
+        <v>12.50942924751286</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.64891953697392</v>
+        <v>3.097414006898687</v>
       </c>
       <c r="C3" t="n">
-        <v>26.00158794697677</v>
+        <v>15.2219981543468</v>
       </c>
       <c r="D3" t="n">
-        <v>90.3846023914826</v>
+        <v>48.98921044191584</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.04865508351838</v>
+        <v>14.07728033119501</v>
       </c>
       <c r="C4" t="n">
-        <v>109.9891222975871</v>
+        <v>52.88871232318417</v>
       </c>
       <c r="D4" t="n">
-        <v>155.8966266958723</v>
+        <v>104.2841863882089</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.30136515413732</v>
+        <v>32.69219855141879</v>
       </c>
       <c r="C5" t="n">
-        <v>186.679325962531</v>
+        <v>168.1733817374786</v>
       </c>
       <c r="D5" t="n">
-        <v>110.1766361090983</v>
+        <v>104.5806741948915</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.66675522656639</v>
+        <v>37.95731148929444</v>
       </c>
       <c r="C6" t="n">
-        <v>172.1965838294821</v>
+        <v>340.6095120067969</v>
       </c>
       <c r="D6" t="n">
-        <v>51.40136455125026</v>
+        <v>68.18630505075798</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.72750041104266</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="C7" t="n">
-        <v>139.356141374722</v>
+        <v>358.9603400945783</v>
       </c>
       <c r="D7" t="n">
-        <v>34.19525428662065</v>
+        <v>44.19631814978291</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.10142311317368</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>105.3120762345553</v>
+        <v>197.2723836913541</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>63.78905708343648</v>
+        <v>77.98905587766234</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>39.85895679242051</v>
+        <v>40.71307729511523</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>33.32542582065798</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>39.26499943135118</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.635992585902686</v>
+        <v>0.5006913291658733</v>
       </c>
       <c r="C2" t="n">
-        <v>3.39488356128547</v>
+        <v>2.325760311360693</v>
       </c>
       <c r="D2" t="n">
-        <v>12.79315433404019</v>
+        <v>9.106691704593414</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.91751749731004</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C3" t="n">
-        <v>28.62776305583699</v>
+        <v>18.03470532701391</v>
       </c>
       <c r="D3" t="n">
-        <v>88.48001184524378</v>
+        <v>53.83904410089508</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.45179353706533</v>
+        <v>22.71764187627119</v>
       </c>
       <c r="C4" t="n">
-        <v>104.4245763099162</v>
+        <v>80.43066241812419</v>
       </c>
       <c r="D4" t="n">
-        <v>166.0174637789526</v>
+        <v>106.6325268967673</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.19122948481243</v>
+        <v>22.87472150895069</v>
       </c>
       <c r="C5" t="n">
-        <v>221.0895829963818</v>
+        <v>271.3305217612123</v>
       </c>
       <c r="D5" t="n">
-        <v>116.7052583423396</v>
+        <v>96.26036240139979</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.5359207399943</v>
+        <v>12.39751000922872</v>
       </c>
       <c r="C6" t="n">
-        <v>203.5928754112951</v>
+        <v>313.1981343565217</v>
       </c>
       <c r="D6" t="n">
-        <v>50.4353248102714</v>
+        <v>59.08943082320704</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>142.590018312511</v>
+        <v>138.6973886651724</v>
       </c>
       <c r="D7" t="n">
-        <v>34.31502750653876</v>
+        <v>34.6743471662931</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>78.94233289848603</v>
+        <v>57.41260574435346</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>30.39687241888974</v>
+        <v>31.06249736236907</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>26.29218526743382</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>33.32542582065798</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.934443887993716</v>
+        <v>0.3671736413883071</v>
       </c>
       <c r="C2" t="n">
-        <v>4.300054944601029</v>
+        <v>2.455351008321272</v>
       </c>
       <c r="D2" t="n">
-        <v>21.78792680034946</v>
+        <v>7.344454575470388</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.7128720064702</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C3" t="n">
-        <v>20.80323385298991</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D3" t="n">
-        <v>80.04679906576369</v>
+        <v>49.28864349171112</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.20555478974863</v>
+        <v>15.08553522345649</v>
       </c>
       <c r="C4" t="n">
-        <v>89.13483756397642</v>
+        <v>59.84439480777282</v>
       </c>
       <c r="D4" t="n">
-        <v>170.8034838371558</v>
+        <v>104.2458982277433</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.64684253504097</v>
+        <v>21.86843011209771</v>
       </c>
       <c r="C5" t="n">
-        <v>209.6522222419064</v>
+        <v>193.2815792735908</v>
       </c>
       <c r="D5" t="n">
-        <v>142.3043297305752</v>
+        <v>98.96016858807852</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.96109961139118</v>
+        <v>12.67927160034756</v>
       </c>
       <c r="C6" t="n">
-        <v>269.3640811096059</v>
+        <v>304.503776687712</v>
       </c>
       <c r="D6" t="n">
-        <v>68.70957657712154</v>
+        <v>61.50453017565419</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.10382857693868</v>
+        <v>3.653083207502381</v>
       </c>
       <c r="C7" t="n">
-        <v>208.1658562176767</v>
+        <v>193.1343171179537</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>122.669375645639</v>
+        <v>68.26091787628073</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>26.28629478120835</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>54.58124536530566</v>
+        <v>28.84374755077128</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>20.63437324785945</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>17.36711688812608</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>13.14952875068177</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>17.23654444346124</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.280599916965341</v>
+        <v>0.3730641276137879</v>
       </c>
       <c r="C2" t="n">
-        <v>2.934443887993716</v>
+        <v>6.385287068421254</v>
       </c>
       <c r="D2" t="n">
-        <v>15.80024755214817</v>
+        <v>11.24690169985146</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.47448724078747</v>
+        <v>2.145118733779281</v>
       </c>
       <c r="C3" t="n">
-        <v>19.14898897133403</v>
+        <v>11.07411410390402</v>
       </c>
       <c r="D3" t="n">
-        <v>79.92408060273283</v>
+        <v>43.90375733391736</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.48334833232148</v>
+        <v>10.55476956835746</v>
       </c>
       <c r="C4" t="n">
-        <v>75.70845596069702</v>
+        <v>44.72057142385071</v>
       </c>
       <c r="D4" t="n">
-        <v>171.9010777705037</v>
+        <v>105.4328312021777</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.34097921967247</v>
+        <v>22.776546738526</v>
       </c>
       <c r="C5" t="n">
-        <v>199.7365704290136</v>
+        <v>149.8146996680633</v>
       </c>
       <c r="D5" t="n">
-        <v>158.994040702771</v>
+        <v>113.4900346109313</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.76992085097032</v>
+        <v>20.85035774279376</v>
       </c>
       <c r="C6" t="n">
-        <v>302.9339621086213</v>
+        <v>307.4421475665227</v>
       </c>
       <c r="D6" t="n">
-        <v>84.1259607769092</v>
+        <v>77.08192099893833</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.18745705824891</v>
+        <v>8.803331663981149</v>
       </c>
       <c r="C7" t="n">
-        <v>267.6332599070187</v>
+        <v>322.2498481896773</v>
       </c>
       <c r="D7" t="n">
-        <v>43.95677170994669</v>
+        <v>41.98051358129786</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>160.0543282233575</v>
+        <v>161.3895051011332</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>62.23593221531803</v>
+        <v>55.80155776168444</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>22.2984356065578</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>16.52575910558656</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.536255230697011</v>
+        <v>0.5065818153913542</v>
       </c>
       <c r="C2" t="n">
-        <v>9.837111996553039</v>
+        <v>16.38929617469625</v>
       </c>
       <c r="D2" t="n">
-        <v>12.83046074680156</v>
+        <v>11.58069591929537</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.74522862298134</v>
+        <v>1.678788574262046</v>
       </c>
       <c r="C3" t="n">
-        <v>15.63924092865169</v>
+        <v>18.38322576202152</v>
       </c>
       <c r="D3" t="n">
-        <v>74.69627407761857</v>
+        <v>42.65693774952391</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.55319128804324</v>
+        <v>7.338564089244907</v>
       </c>
       <c r="C4" t="n">
-        <v>62.70324412253954</v>
+        <v>35.83771819582557</v>
       </c>
       <c r="D4" t="n">
-        <v>171.8372641697277</v>
+        <v>103.7226267013798</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.19371706403545</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="C5" t="n">
-        <v>173.7447999590793</v>
+        <v>116.0671223345792</v>
       </c>
       <c r="D5" t="n">
-        <v>177.2054606165493</v>
+        <v>124.5837836689203</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.4366096576119</v>
+        <v>25.72080810356219</v>
       </c>
       <c r="C6" t="n">
-        <v>312.7956177977806</v>
+        <v>272.8659751706543</v>
       </c>
       <c r="D6" t="n">
-        <v>105.0568218314512</v>
+        <v>92.01528532823657</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.21899615797182</v>
+        <v>16.04961146902685</v>
       </c>
       <c r="C7" t="n">
-        <v>333.867850521734</v>
+        <v>384.3522627172177</v>
       </c>
       <c r="D7" t="n">
-        <v>52.99964981376406</v>
+        <v>52.939763203805</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>232.988365171853</v>
+        <v>288.1478599349601</v>
       </c>
       <c r="D8" t="n">
-        <v>36.88426124855267</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>111.492178032789</v>
+        <v>122.5859270907779</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>24.07343545583603</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>45.98015372839937</v>
+        <v>43.84485247166256</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.25371718051895</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.115887286830128</v>
+        <v>6.365652114336318</v>
       </c>
       <c r="C2" t="n">
-        <v>4.442408361716817</v>
+        <v>11.03288070032565</v>
       </c>
       <c r="D2" t="n">
-        <v>7.319910882864218</v>
+        <v>10.80609698064464</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.558434517267188</v>
+        <v>0.8325220532012952</v>
       </c>
       <c r="C2" t="n">
-        <v>5.665666001208343</v>
+        <v>12.35038611942488</v>
       </c>
       <c r="D2" t="n">
-        <v>9.545532928391737</v>
+        <v>10.15814349584175</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.74585051778709</v>
+        <v>1.65915362017711</v>
       </c>
       <c r="C3" t="n">
-        <v>24.52896639060656</v>
+        <v>40.16329858073701</v>
       </c>
       <c r="D3" t="n">
-        <v>79.73754853892594</v>
+        <v>41.80772598535042</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.00509833163304</v>
+        <v>5.322054304721959</v>
       </c>
       <c r="C4" t="n">
-        <v>92.70839920743479</v>
+        <v>40.48334833232148</v>
       </c>
       <c r="D4" t="n">
-        <v>175.525690294583</v>
+        <v>101.6678287563912</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.88916998707391</v>
+        <v>16.22338081267855</v>
       </c>
       <c r="C5" t="n">
-        <v>263.1329284307514</v>
+        <v>92.16156573616934</v>
       </c>
       <c r="D5" t="n">
-        <v>158.9694970101648</v>
+        <v>130.3760951239765</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.00507296943726</v>
+        <v>26.1635763181775</v>
       </c>
       <c r="C6" t="n">
-        <v>278.1389420901639</v>
+        <v>235.4721868635975</v>
       </c>
       <c r="D6" t="n">
-        <v>81.8316163920844</v>
+        <v>106.9486496575348</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.809001166028376</v>
+        <v>22.27781890476862</v>
       </c>
       <c r="C7" t="n">
-        <v>163.8497648479756</v>
+        <v>389.3228513438194</v>
       </c>
       <c r="D7" t="n">
-        <v>32.63820242768521</v>
+        <v>63.36003333668064</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C8" t="n">
-        <v>82.11337798320321</v>
+        <v>387.368191664664</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>35.05624702324509</v>
+        <v>221.985918650359</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>26.07031028627404</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>22.06477965294707</v>
+        <v>84.41557634966199</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>22.34948648717864</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.86995163914969</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.886199381765381</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.711808143307943</v>
+        <v>6.90364985626357</v>
       </c>
       <c r="C2" t="n">
-        <v>5.114905539125882</v>
+        <v>8.096473316923445</v>
       </c>
       <c r="D2" t="n">
-        <v>10.08745766113598</v>
+        <v>16.55521153671396</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.87285582453342</v>
+        <v>10.50470043544087</v>
       </c>
       <c r="C3" t="n">
-        <v>11.36863841517807</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D3" t="n">
-        <v>9.576948854927634</v>
+        <v>10.39670818797372</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39910580118038</v>
+        <v>11.67751693001316</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14825978265024</v>
+        <v>59.9445869074009</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576365388374163</v>
+        <v>0.7785011286675441</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.060909415392308</v>
+        <v>3.659955441432109</v>
       </c>
       <c r="C2" t="n">
-        <v>6.429465715112362</v>
+        <v>8.730682333866884</v>
       </c>
       <c r="D2" t="n">
-        <v>16.02703127182918</v>
+        <v>21.72313145186917</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.1890196430299</v>
+        <v>19.02627050830318</v>
       </c>
       <c r="C3" t="n">
-        <v>16.83206438931157</v>
+        <v>28.36759991421159</v>
       </c>
       <c r="D3" t="n">
-        <v>15.73250696055514</v>
+        <v>22.34948648717864</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.7116692745877</v>
+        <v>12.94139823738145</v>
       </c>
       <c r="C4" t="n">
-        <v>18.14858806070654</v>
+        <v>35.93981995706723</v>
       </c>
       <c r="D4" t="n">
-        <v>20.08852152429823</v>
+        <v>19.69287719948677</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4454376343458</v>
+        <v>13.62701948754389</v>
       </c>
       <c r="C21" t="n">
-        <v>86.169283644245</v>
+        <v>73.74622310906105</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251671080914905</v>
+        <v>1.603178763240458</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.485605260703677</v>
+        <v>2.661518026213103</v>
       </c>
       <c r="C2" t="n">
-        <v>5.027529993447916</v>
+        <v>9.699667317958486</v>
       </c>
       <c r="D2" t="n">
-        <v>19.23047403078652</v>
+        <v>19.40129813132546</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.15604113171301</v>
+        <v>15.55579237379071</v>
       </c>
       <c r="C3" t="n">
-        <v>21.79479903427919</v>
+        <v>32.00006641992479</v>
       </c>
       <c r="D3" t="n">
-        <v>24.90203051822035</v>
+        <v>35.19565519724815</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.20262524216912</v>
+        <v>27.00591584842126</v>
       </c>
       <c r="C4" t="n">
-        <v>32.09824119034946</v>
+        <v>57.70025782169779</v>
       </c>
       <c r="D4" t="n">
-        <v>23.27920156310037</v>
+        <v>26.82723776624834</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.51099183229385</v>
+        <v>11.78097245096173</v>
       </c>
       <c r="C5" t="n">
-        <v>21.69662426385451</v>
+        <v>41.87153958612647</v>
       </c>
       <c r="D5" t="n">
-        <v>30.0414797499524</v>
+        <v>27.02260555939346</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74466133130946</v>
+        <v>14.83357859693901</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1424341209877</v>
+        <v>87.35329618197416</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023398399392836</v>
+        <v>2.472263099489834</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.802529842726149</v>
+        <v>2.451424017504285</v>
       </c>
       <c r="C2" t="n">
-        <v>3.932881303212722</v>
+        <v>12.6508009169244</v>
       </c>
       <c r="D2" t="n">
-        <v>27.5164246546296</v>
+        <v>18.58939277991335</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.17920216598743</v>
+        <v>11.97241325328985</v>
       </c>
       <c r="C3" t="n">
-        <v>20.45962215650353</v>
+        <v>35.48527077000096</v>
       </c>
       <c r="D3" t="n">
-        <v>33.9782880439821</v>
+        <v>42.54894550205677</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.52467954689108</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="C4" t="n">
-        <v>44.8737240657132</v>
+        <v>70.93519862264904</v>
       </c>
       <c r="D4" t="n">
-        <v>29.9030533236536</v>
+        <v>38.4285503873329</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.4392264388926</v>
+        <v>26.65445017030091</v>
       </c>
       <c r="C5" t="n">
-        <v>42.36241343824987</v>
+        <v>78.78525326580655</v>
       </c>
       <c r="D5" t="n">
-        <v>31.80862561759666</v>
+        <v>30.40963513904496</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.74719211838983</v>
+        <v>10.50568218314512</v>
       </c>
       <c r="C6" t="n">
-        <v>23.82898027747859</v>
+        <v>41.09694064747573</v>
       </c>
       <c r="D6" t="n">
-        <v>37.91705983342032</v>
+        <v>33.73088762251191</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>25.70215489718149</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.574764375340887</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07932865166267</v>
+        <v>16.06948774624188</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9460964417993</v>
+        <v>100.6457390422517</v>
       </c>
       <c r="D21" t="n">
-        <v>6.887363295871493</v>
+        <v>3.383050051840395</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.893832379221102</v>
+        <v>2.166717183272711</v>
       </c>
       <c r="C2" t="n">
-        <v>12.43088943117311</v>
+        <v>14.67123769226433</v>
       </c>
       <c r="D2" t="n">
-        <v>39.66751599009237</v>
+        <v>14.47685164682347</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.13778883595982</v>
+        <v>10.0187353218387</v>
       </c>
       <c r="C3" t="n">
-        <v>16.4050041379642</v>
+        <v>43.15762907868979</v>
       </c>
       <c r="D3" t="n">
-        <v>44.52716712611409</v>
+        <v>47.21224709722911</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.90082778633785</v>
+        <v>26.06147455693583</v>
       </c>
       <c r="C4" t="n">
-        <v>40.62373825402877</v>
+        <v>80.71144226153878</v>
       </c>
       <c r="D4" t="n">
-        <v>34.34447993766616</v>
+        <v>50.42550733322892</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.64124548178919</v>
+        <v>34.97476196379262</v>
       </c>
       <c r="C5" t="n">
-        <v>47.68839473378882</v>
+        <v>105.7096840547753</v>
       </c>
       <c r="D5" t="n">
-        <v>28.78975142703772</v>
+        <v>36.98734475749859</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.7132318593687</v>
+        <v>23.06419881587032</v>
       </c>
       <c r="C6" t="n">
-        <v>31.83905979642831</v>
+        <v>84.60898064739862</v>
       </c>
       <c r="D6" t="n">
-        <v>30.39000018496002</v>
+        <v>35.54221213684728</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>17.96598298771663</v>
+        <v>38.92629647338602</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.069705925700821</v>
+        <v>17.32716128931699</v>
       </c>
       <c r="C21" t="n">
-        <v>67.1622062941578</v>
+        <v>114.3592645094921</v>
       </c>
       <c r="D21" t="n">
-        <v>5.302279444275616</v>
+        <v>4.331790322329248</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.406484607287184</v>
+        <v>4.156719779780995</v>
       </c>
       <c r="C2" t="n">
-        <v>6.515859513086081</v>
+        <v>9.403179511275949</v>
       </c>
       <c r="D2" t="n">
-        <v>42.39088412167303</v>
+        <v>22.76574751377929</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.15313694632928</v>
+        <v>8.59029241215959</v>
       </c>
       <c r="C3" t="n">
-        <v>37.48803608666446</v>
+        <v>50.22621254926682</v>
       </c>
       <c r="D3" t="n">
-        <v>68.24619166071703</v>
+        <v>47.46259276181205</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.24764676784423</v>
+        <v>22.64106555533994</v>
       </c>
       <c r="C4" t="n">
-        <v>41.01938257884023</v>
+        <v>93.67836593923064</v>
       </c>
       <c r="D4" t="n">
-        <v>50.48932093400496</v>
+        <v>60.20175097211866</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.17615911188346</v>
+        <v>36.88916998707391</v>
       </c>
       <c r="C5" t="n">
-        <v>64.79534848028949</v>
+        <v>127.2590461629928</v>
       </c>
       <c r="D5" t="n">
-        <v>35.41654843070369</v>
+        <v>45.65126824747669</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.1321193339126</v>
+        <v>34.37491411649783</v>
       </c>
       <c r="C6" t="n">
-        <v>58.12339108222817</v>
+        <v>124.6593782421473</v>
       </c>
       <c r="D6" t="n">
-        <v>32.88560284915541</v>
+        <v>38.56108632740622</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.54004335279375</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="C7" t="n">
-        <v>34.49468733641593</v>
+        <v>77.6729331168949</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>22.19731559302038</v>
+        <v>37.88564390688441</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>46.02335062738621</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.295678699223436</v>
+        <v>17.71381202075569</v>
       </c>
       <c r="C21" t="n">
-        <v>77.516586179249</v>
+        <v>126.6537559484032</v>
       </c>
       <c r="D21" t="n">
-        <v>6.383718861820507</v>
+        <v>5.314143606226706</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.513094196422587</v>
+        <v>3.617740290149496</v>
       </c>
       <c r="C2" t="n">
-        <v>10.14930776650353</v>
+        <v>5.942518853805943</v>
       </c>
       <c r="D2" t="n">
-        <v>35.18485597250144</v>
+        <v>18.02979658849267</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.24854640009046</v>
+        <v>13.27322896141688</v>
       </c>
       <c r="C3" t="n">
-        <v>30.03166227290993</v>
+        <v>68.90887136108363</v>
       </c>
       <c r="D3" t="n">
-        <v>86.32507563442203</v>
+        <v>53.14200323087985</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.93080430127976</v>
+        <v>17.71465557542945</v>
       </c>
       <c r="C4" t="n">
-        <v>72.6709285637574</v>
+        <v>120.1737729814436</v>
       </c>
       <c r="D4" t="n">
-        <v>72.8368439257751</v>
+        <v>56.39846036586651</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.57639338004667</v>
+        <v>19.36497346626834</v>
       </c>
       <c r="C5" t="n">
-        <v>71.27488332831845</v>
+        <v>74.49010705972675</v>
       </c>
       <c r="D5" t="n">
-        <v>46.16668579220627</v>
+        <v>36.17740290149497</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.79251674370121</v>
+        <v>10.86794708601219</v>
       </c>
       <c r="C6" t="n">
-        <v>83.32092765942681</v>
+        <v>51.15985461600555</v>
       </c>
       <c r="D6" t="n">
-        <v>36.99127174831558</v>
+        <v>25.80131141531043</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.56484908730718</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>61.98264130762237</v>
+        <v>26.58965482182061</v>
       </c>
       <c r="D7" t="n">
-        <v>35.75230614555609</v>
+        <v>26.70942804173872</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>35.13184159647211</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>26.40312275801371</v>
+        <v>25.62656032395449</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
         <v>35.89465956267188</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.508247247797547</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>87.28337425564648</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.508247247797547</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
